--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9261</v>
+        <v>9334</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1776</v>
+        <v>1818</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2426</v>
+        <v>2484</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3712</v>
+        <v>3785</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4287</v>
+        <v>4296</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1886,11 +1886,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1978,11 +1978,11 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>931</v>
+        <v>951</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>931</v>
+        <v>951</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9261</v>
+        <v>9334</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1776</v>
+        <v>1818</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2426</v>
+        <v>2484</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3712</v>
+        <v>3785</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1071</v>
+        <v>1081</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4287</v>
+        <v>4296</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4194,11 +4194,11 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4286,11 +4286,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9334</v>
+        <v>9401</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,11 +1012,11 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2484</v>
+        <v>2536</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3785</v>
+        <v>3838</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1407,30 +1407,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.03 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>110</v>
+        <v>2111</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/AIIyV3Nm1700710851214.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>444</v>
+        <v>189</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1780,38 +1780,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4296</v>
+        <v>453</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1821,43 +1821,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>67</v>
+        <v>4306</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1872,25 +1872,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·第十五届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1913,30 +1913,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1964,36 +1964,82 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>298</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>北京·第十六届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>62</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="F35" t="n">
+        <v>98</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -2088,11 +2134,11 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2134,7 +2180,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2226,7 +2272,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2272,7 +2318,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2382,7 +2428,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2428,7 +2474,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2460,7 +2506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2538,7 +2584,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2630,7 +2676,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>951</v>
+        <v>960</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2676,11 +2722,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -2722,7 +2768,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2860,7 +2906,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2906,7 +2952,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2952,7 +2998,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9334</v>
+        <v>9401</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2998,7 +3044,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3044,7 +3090,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3090,7 +3136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3136,7 +3182,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1818</v>
+        <v>1868</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3182,7 +3228,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3228,11 +3274,11 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -3320,7 +3366,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2484</v>
+        <v>2536</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3366,7 +3412,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3412,7 +3458,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3785</v>
+        <v>3838</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3458,7 +3504,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3504,7 +3550,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3550,7 +3596,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3596,7 +3642,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3642,7 +3688,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3669,30 +3715,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.03 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -3700,12 +3746,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3780,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3780,7 +3826,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3826,7 +3872,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3872,7 +3918,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3918,7 +3964,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>507</v>
+        <v>532</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3964,11 +4010,11 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>110</v>
+        <v>2111</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -3981,7 +4027,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/AIIyV3Nm1700710851214.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4056,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4042,25 +4088,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>444</v>
+        <v>189</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -4068,12 +4114,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -4088,38 +4134,38 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4296</v>
+        <v>453</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4129,43 +4175,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>67</v>
+        <v>4306</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4180,25 +4226,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·第十五届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -4206,12 +4252,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4221,30 +4267,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -4252,12 +4298,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4272,25 +4318,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>62</v>
+        <v>298</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -4298,12 +4344,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4313,41 +4359,87 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>北京·第十六届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:00-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>98</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>15</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F42" t="n">
+        <v>17</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="H41" t="b">
+      <c r="H42" t="b">
         <v>1</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9401</v>
+        <v>9452</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1868</v>
+        <v>1922</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>118</v>
+        <v>680</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2536</v>
+        <v>2582</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3838</v>
+        <v>3882</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1376,11 +1376,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 16:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/FJSimcpk1704252061898.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2111</v>
+        <v>2132</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4306</v>
+        <v>4314</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2115,30 +2115,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>北京·Nanawo Akari  七音阿卡丽-演唱会</t>
+          <t xml:space="preserve">北京·戳心场！向着疾风前进《你的名字》《火影忍者》《鬼灭之刃》热血动漫名曲ACG音乐演奏会 </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>建国门外郎家园10号61幢一层A3-06、二层A3-06 East live</t>
+          <t>三里屯SOHO下沉广场最南端,6号商场B1层 三里屯·爱乐汇艺术空间</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.25 20:00-01.25 22:00</t>
+          <t>2024.01.26 19:30-01.26 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80452</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CoNbgCpO1703644783043.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/bZRwDkbn1704340285463.jpeg</t>
         </is>
       </c>
     </row>
@@ -2161,30 +2161,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京·戳心场！向着疾风前进《你的名字》《火影忍者》《鬼灭之刃》热血动漫名曲ACG音乐演奏会 </t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>三里屯SOHO下沉广场最南端,6号商场B1层 三里屯·爱乐汇艺术空间</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80452</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/bZRwDkbn1704340285463.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2207,30 +2207,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>东郎电影创意产业园 东郎电影创意产业园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.03.03 13:00-03.03 16:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
         </is>
       </c>
     </row>
@@ -2253,87 +2253,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>
@@ -2428,7 +2382,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2474,7 +2428,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2506,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2584,7 +2538,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2630,7 +2584,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2676,7 +2630,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>960</v>
+        <v>969</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2703,30 +2657,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·Nanawo Akari  七音阿卡丽-演唱会</t>
+          <t xml:space="preserve">北京·戳心场！向着疾风前进《你的名字》《火影忍者》《鬼灭之刃》热血动漫名曲ACG音乐演奏会 </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>建国门外郎家园10号61幢一层A3-06、二层A3-06 East live</t>
+          <t>三里屯SOHO下沉广场最南端,6号商场B1层 三里屯·爱乐汇艺术空间</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.25 20:00-01.25 22:00</t>
+          <t>2024.01.26 19:30-01.26 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -2734,12 +2688,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80452</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CoNbgCpO1703644783043.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/bZRwDkbn1704340285463.jpeg</t>
         </is>
       </c>
     </row>
@@ -2749,30 +2703,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京·戳心场！向着疾风前进《你的名字》《火影忍者》《鬼灭之刃》热血动漫名曲ACG音乐演奏会 </t>
+          <t xml:space="preserve"> 北京·第十四届IJOY漫展x CGF游戏节——村上幸平专场见面会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>三里屯SOHO下沉广场最南端,6号商场B1层 三里屯·爱乐汇艺术空间</t>
+          <t>国家会议中心 国家会议中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:00</t>
+          <t>2024.01.27 09:00-01.27 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -2780,12 +2734,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80452</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79457</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/bZRwDkbn1704340285463.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/rFjnjEN51701918358910.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,25 +2754,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·第十四届IJOY漫展x CGF游戏节——村上幸平专场见面会</t>
+          <t>北京·原神x穹铁北京同人嘉年华6th</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.27 17:00</t>
+          <t>2024.01.27 09:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>93</v>
+        <v>834</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -2826,12 +2780,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79457</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/rFjnjEN51701918358910.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2800,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·原神x穹铁北京同人嘉年华6th</t>
+          <t>北京·国乙同好嘉年华5th</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2860,7 +2814,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>832</v>
+        <v>510</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2872,12 +2826,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2892,25 +2846,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·国乙同好嘉年华5th</t>
+          <t>北京·第十四届IJOY漫展x CGF游戏节——青柳尊哉专场见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>国家会议中心 国家会议中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.01.27 09:00-01.27 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>509</v>
+        <v>281</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -2918,12 +2872,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79061</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/ghxcik8i1701078987783.jpeg</t>
         </is>
       </c>
     </row>
@@ -2938,25 +2892,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——青柳尊哉专场见面会</t>
+          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.27 17:00</t>
+          <t>2024.01.27 09:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>279</v>
+        <v>9452</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -2964,12 +2918,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79061</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/ghxcik8i1701078987783.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
         </is>
       </c>
     </row>
@@ -2979,30 +2933,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
+          <t>北京·第十四届IJOY漫展x CGF游戏节——岩永彻也专场见面会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>国家会议中心 国家会议中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.01.28 09:00-01.28 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9401</v>
+        <v>236</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>598</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -3010,12 +2964,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
         </is>
       </c>
     </row>
@@ -3025,30 +2979,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——岩永彻也专场见面会</t>
+          <t>北京·跨次元派对2.0童话奇妙夜</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.28 09:00-01.28 17:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -3056,12 +3010,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -3071,30 +3025,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>688</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -3102,12 +3056,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -3122,25 +3076,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>683</v>
+        <v>1922</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -3148,12 +3102,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3122,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3182,11 +3136,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1868</v>
+        <v>43</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -3194,12 +3148,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -3214,25 +3168,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>680</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -3240,12 +3194,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -3255,30 +3209,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -3286,12 +3240,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -3301,30 +3255,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2582</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -3332,12 +3286,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3306,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2536</v>
+        <v>126</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -3378,12 +3332,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3352,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3412,24 +3366,24 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>122</v>
+        <v>3882</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3439,43 +3393,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3838</v>
+        <v>300</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3490,25 +3444,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>291</v>
+        <v>135</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -3516,12 +3470,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3531,30 +3485,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -3562,12 +3516,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3582,25 +3536,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -3608,12 +3562,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,30 +3577,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -3654,12 +3608,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3674,21 +3628,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 16:30</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3700,12 +3654,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/FJSimcpk1704252061898.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3715,30 +3669,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东郎电影创意产业园 东郎电影创意产业园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.03 13:00-03.03 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -3746,12 +3700,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
         </is>
       </c>
     </row>
@@ -3761,30 +3715,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -3792,12 +3746,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3812,25 +3766,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -3838,12 +3792,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3853,30 +3807,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -3884,12 +3838,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3858,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>251</v>
+        <v>555</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3904,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3964,11 +3918,11 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>532</v>
+        <v>2132</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -3976,12 +3930,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,12 +3945,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4006,15 +3960,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2111</v>
+        <v>1090</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -4022,12 +3976,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -4042,12 +3996,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4056,24 +4010,24 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1086</v>
+        <v>191</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -4088,25 +4042,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>189</v>
+        <v>463</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -4114,12 +4068,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4134,38 +4088,38 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>453</v>
+        <v>4314</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4175,43 +4129,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4306</v>
+        <v>67</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4226,25 +4180,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -4252,12 +4206,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4267,30 +4221,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>110</v>
+        <v>322</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -4298,12 +4252,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4318,25 +4272,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>298</v>
+        <v>130</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -4344,12 +4298,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
       </c>
     </row>
@@ -4359,87 +4313,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY国际动漫游戏狂欢节/CGF游戏节</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>680</t>
         </is>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>17</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H42" t="b">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -506,22 +501,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G2" t="n">
+        <v>88</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79158</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79158</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/zUtfsyPj1701240093229.jpeg</t>
         </is>
@@ -533,43 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·第十四届IJOY漫展x CGF游戏节——村上幸平专场见面会</t>
+          <t>北京·我的爸爸是条龙主题快闪店——线下集章之旅</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>复兴门外大街15号 长安商场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.27 17:00</t>
+          <t>2024.01.26 10:00-02.26 22:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>93</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81427</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79457</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/rFjnjEN51701918358910.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/A1VDdvxs1706178337277.jpeg</t>
         </is>
       </c>
     </row>
@@ -598,22 +583,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
         </is>
@@ -644,22 +626,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
         </is>
@@ -676,38 +655,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——青柳尊哉专场见面会</t>
+          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.27 17:00</t>
+          <t>2024.01.27 09:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>281</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80922</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79061</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/ghxcik8i1701078987783.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
         </is>
       </c>
     </row>
@@ -736,22 +712,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9452</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>9606</v>
+      </c>
+      <c r="G7" t="n">
+        <v>238</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
         </is>
@@ -782,22 +753,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
         </is>
@@ -828,22 +796,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G9" t="n">
+        <v>158</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
@@ -874,22 +837,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>688</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>708</v>
+      </c>
+      <c r="G10" t="n">
+        <v>68</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
@@ -920,22 +878,17 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1922</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>2093</v>
+      </c>
+      <c r="G11" t="n">
+        <v>75</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
@@ -966,22 +919,17 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="G12" t="n">
+        <v>158</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
@@ -1012,22 +960,17 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>680</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>1616</v>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
@@ -1058,22 +1001,17 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2582</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>2714</v>
+      </c>
+      <c r="G14" t="n">
+        <v>75</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
@@ -1104,22 +1042,17 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>126</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="G15" t="n">
+        <v>70</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
@@ -1150,22 +1083,17 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3882</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
+        <v>4045</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
@@ -1196,22 +1124,17 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="G17" t="n">
+        <v>60</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
@@ -1242,22 +1165,17 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>135</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
@@ -1288,22 +1206,17 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>123</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>131</v>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
@@ -1334,22 +1247,17 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>204</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="G20" t="n">
+        <v>55</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
@@ -1380,22 +1288,17 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>234</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="G21" t="n">
+        <v>65</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
@@ -1426,22 +1329,17 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G22" t="n">
+        <v>65</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
@@ -1474,20 +1372,15 @@
       <c r="F23" t="n">
         <v>79</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
@@ -1518,22 +1411,17 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="G24" t="n">
+        <v>93</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
@@ -1564,22 +1452,17 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>256</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>277</v>
+      </c>
+      <c r="G25" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
@@ -1610,22 +1493,17 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>555</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>1</v>
+        <v>3796</v>
+      </c>
+      <c r="G26" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
@@ -1642,12 +1520,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1656,24 +1534,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2132</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>78</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1556,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1698,28 +1571,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1090</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>1</v>
+        <v>3292</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1602,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1748,24 +1616,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>191</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>1102</v>
+      </c>
+      <c r="G29" t="n">
+        <v>58</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1780,38 +1643,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>463</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1826,38 +1684,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4314</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>1</v>
+        <v>488</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1867,43 +1720,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>67</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
+        <v>4330</v>
+      </c>
+      <c r="G32" t="n">
+        <v>75</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1918,38 +1766,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1959,43 +1804,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>322</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -2010,36 +1850,72 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>386</v>
+      </c>
+      <c r="G35" t="n">
+        <v>75</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>130</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="F36" t="n">
+        <v>247</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -2056,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,15 +1971,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2115,43 +1986,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京·戳心场！向着疾风前进《你的名字》《火影忍者》《鬼灭之刃》热血动漫名曲ACG音乐演奏会 </t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>三里屯SOHO下沉广场最南端,6号商场B1层 三里屯·爱乐汇艺术空间</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>180</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80452</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/bZRwDkbn1704340285463.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2161,43 +2027,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>东郎电影创意产业园 东郎电影创意产业园</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.03.03 13:00-03.03 16:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
         </is>
       </c>
     </row>
@@ -2207,43 +2068,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>280</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2128,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>680</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>
@@ -2304,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2343,15 +2194,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2382,22 +2228,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>185</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>201</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79831</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79831</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/SlgzFC7D1702967178610.jpeg</t>
         </is>
@@ -2428,22 +2269,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>969</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>993</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80186</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80186</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/yf8VthSg1703498739957.jpeg</t>
         </is>
@@ -2460,7 +2296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2499,15 +2335,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2538,22 +2369,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>185</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>201</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79831</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79831</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/SlgzFC7D1702967178610.jpeg</t>
         </is>
@@ -2584,22 +2410,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79158</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79158</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/zUtfsyPj1701240093229.jpeg</t>
         </is>
@@ -2630,22 +2451,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>969</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>993</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80186</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80186</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/yf8VthSg1703498739957.jpeg</t>
         </is>
@@ -2662,38 +2478,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">北京·戳心场！向着疾风前进《你的名字》《火影忍者》《鬼灭之刃》热血动漫名曲ACG音乐演奏会 </t>
+          <t>北京·我的爸爸是条龙主题快闪店——线下集章之旅</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>三里屯SOHO下沉广场最南端,6号商场B1层 三里屯·爱乐汇艺术空间</t>
+          <t>复兴门外大街15号 长安商场</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:00</t>
+          <t>2024.01.26 10:00-02.26 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>68</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81427</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80452</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/bZRwDkbn1704340285463.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/A1VDdvxs1706178337277.jpeg</t>
         </is>
       </c>
     </row>
@@ -2708,38 +2519,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·第十四届IJOY漫展x CGF游戏节——村上幸平专场见面会</t>
+          <t>北京·原神x穹铁北京同人嘉年华6th</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.27 17:00</t>
+          <t>2024.01.27 09:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>840</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79457</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/rFjnjEN51701918358910.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2562,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·原神x穹铁北京同人嘉年华6th</t>
+          <t>北京·国乙同好嘉年华5th</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2768,24 +2576,21 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>834</v>
+        <v>508</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2605,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·国乙同好嘉年华5th</t>
+          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2814,24 +2619,21 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>510</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H8" t="b">
-        <v>0</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80922</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,38 +2648,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——青柳尊哉专场见面会</t>
+          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.27 17:00</t>
+          <t>2024.01.27 09:00-01.29 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>281</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>9606</v>
+      </c>
+      <c r="G9" t="n">
+        <v>238</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79061</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/ghxcik8i1701078987783.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
         </is>
       </c>
     </row>
@@ -2887,43 +2684,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
+          <t>北京·第十四届IJOY漫展x CGF游戏节——岩永彻也专场见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>国家会议中心 国家会议中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.01.28 09:00-01.28 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9452</v>
+        <v>241</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
         </is>
       </c>
     </row>
@@ -2933,43 +2727,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——岩永彻也专场见面会</t>
+          <t>北京·跨次元派对2.0童话奇妙夜</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.28 09:00-01.28 17:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>236</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>158</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -2979,43 +2768,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>708</v>
+      </c>
+      <c r="G12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -3030,38 +2814,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>688</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>2093</v>
+      </c>
+      <c r="G13" t="n">
+        <v>75</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -3076,7 +2855,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3090,24 +2869,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1922</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="G14" t="n">
+        <v>158</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -3122,38 +2896,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>1616</v>
+      </c>
+      <c r="G15" t="n">
+        <v>59</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -3163,43 +2932,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>680</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>180</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -3209,43 +2973,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>2714</v>
+      </c>
+      <c r="G17" t="n">
+        <v>75</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3019,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2582</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="G18" t="n">
+        <v>70</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3060,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3320,24 +3074,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>126</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>4045</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3347,43 +3096,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3882</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
+        <v>329</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3398,38 +3142,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3439,43 +3178,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>135</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>131</v>
+      </c>
+      <c r="G22" t="n">
+        <v>48</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3490,38 +3224,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>123</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>217</v>
+      </c>
+      <c r="G23" t="n">
+        <v>55</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3531,43 +3260,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>204</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="G24" t="n">
+        <v>65</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3582,38 +3306,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>234</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G25" t="n">
+        <v>65</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3623,43 +3342,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东郎电影创意产业园 东郎电影创意产业园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.03 13:00-03.03 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="G26" t="n">
+        <v>88</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
         </is>
       </c>
     </row>
@@ -3669,43 +3383,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>18</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="G27" t="n">
+        <v>60</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3720,38 +3429,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>79</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="G28" t="n">
+        <v>93</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3761,43 +3465,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>66</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>277</v>
+      </c>
+      <c r="G29" t="n">
+        <v>60</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3812,38 +3511,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>256</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
+        <v>3796</v>
+      </c>
+      <c r="G30" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3552,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3872,24 +3566,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>555</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>78</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3918,22 +3607,17 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2132</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>1</v>
+        <v>3292</v>
+      </c>
+      <c r="G32" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
@@ -3964,22 +3648,17 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1090</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>1</v>
+        <v>1102</v>
+      </c>
+      <c r="G33" t="n">
+        <v>58</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
@@ -4010,22 +3689,17 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>191</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
+        <v>197</v>
+      </c>
+      <c r="G34" t="n">
+        <v>75</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
@@ -4056,22 +3730,17 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>463</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
+        <v>488</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
@@ -4102,22 +3771,17 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4314</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H36" t="b">
-        <v>1</v>
+        <v>4330</v>
+      </c>
+      <c r="G36" t="n">
+        <v>75</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
@@ -4148,22 +3812,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>不可售</t>
         </is>
       </c>
-      <c r="H37" t="b">
-        <v>0</v>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
@@ -4194,22 +3855,17 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>146</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
+        <v>267</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
@@ -4240,22 +3896,17 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>322</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
+        <v>386</v>
+      </c>
+      <c r="G39" t="n">
+        <v>75</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
@@ -4286,22 +3937,17 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>130</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
+        <v>247</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -4313,41 +3959,77 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.05.18 20:00-05.18 22:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>280</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>19</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="H41" t="b">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="F42" t="n">
+        <v>24</v>
+      </c>
+      <c r="G42" t="n">
+        <v>680</v>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -712,10 +712,12 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9606</v>
-      </c>
-      <c r="G7" t="n">
-        <v>238</v>
+        <v>9617</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -734,40 +736,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——岩永彻也专场见面会</t>
+          <t>北京·跨次元派对2.0童话奇妙夜</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.28 09:00-01.28 17:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>241</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="G8" t="n">
+        <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -777,38 +777,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>718</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -823,33 +823,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>708</v>
+        <v>2161</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2093</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -905,33 +905,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>1643</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -941,38 +941,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1616</v>
+        <v>2766</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -987,33 +987,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2714</v>
+        <v>142</v>
       </c>
       <c r="G14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>134</v>
+        <v>4120</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>19.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1064,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4045</v>
+        <v>345</v>
       </c>
       <c r="G16" t="n">
-        <v>19.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -1110,33 +1110,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>329</v>
+        <v>169</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1146,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="G18" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -1192,33 +1192,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>131</v>
+        <v>523</v>
       </c>
       <c r="G19" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1228,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="G20" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -1274,33 +1274,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>239</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1310,38 +1310,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1356,33 +1356,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1392,38 +1392,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1438,33 +1438,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>277</v>
+        <v>3963</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>49.9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3796</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>49.9</v>
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3446</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1571,23 +1571,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3292</v>
+        <v>1106</v>
       </c>
       <c r="G28" t="n">
-        <v>29.9</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1102</v>
+        <v>203</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1643,33 +1643,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>197</v>
+        <v>505</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>488</v>
+        <v>4338</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1720,38 +1720,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4330</v>
-      </c>
-      <c r="G32" t="n">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1766,35 +1768,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>73</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>320</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1804,38 +1804,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>267</v>
+        <v>422</v>
       </c>
       <c r="G34" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>247</v>
-      </c>
-      <c r="G36" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -2005,7 +1964,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2046,7 +2005,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2228,7 +2187,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2269,7 +2228,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>993</v>
+        <v>1009</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2296,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2369,7 +2328,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2410,7 +2369,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2451,7 +2410,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>993</v>
+        <v>1009</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2533,7 +2492,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2576,7 +2535,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2619,7 +2578,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2662,10 +2621,12 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9606</v>
-      </c>
-      <c r="G9" t="n">
-        <v>238</v>
+        <v>9617</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2684,40 +2645,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展x CGF游戏节——岩永彻也专场见面会</t>
+          <t>北京·跨次元派对2.0童话奇妙夜</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>国家会议中心 国家会议中心</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.28 09:00-01.28 17:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>39</v>
+      </c>
+      <c r="G10" t="n">
+        <v>158</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79059</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/4QhCuqq21701079008566.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -2727,38 +2686,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>718</v>
       </c>
       <c r="G11" t="n">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -2773,33 +2732,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>708</v>
+        <v>2161</v>
       </c>
       <c r="G12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2773,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2828,19 +2787,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2093</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -2855,33 +2814,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>1643</v>
       </c>
       <c r="G14" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -2891,38 +2850,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1616</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2932,38 +2891,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2766</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -2978,33 +2937,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2714</v>
+        <v>142</v>
       </c>
       <c r="G17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3019,7 +2978,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3033,19 +2992,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>134</v>
+        <v>4121</v>
       </c>
       <c r="G18" t="n">
-        <v>70</v>
+        <v>19.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3055,38 +3014,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4045</v>
+        <v>345</v>
       </c>
       <c r="G19" t="n">
-        <v>19.9</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3101,33 +3060,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>329</v>
+        <v>169</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3137,38 +3096,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="G21" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3183,33 +3142,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>131</v>
+        <v>523</v>
       </c>
       <c r="G22" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3219,38 +3178,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="G23" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3265,33 +3224,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>239</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3301,38 +3260,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东郎电影创意产业园 东郎电影创意产业园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.03 13:00-03.03 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
         </is>
       </c>
     </row>
@@ -3342,38 +3301,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3388,33 +3347,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3424,38 +3383,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="G28" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3470,33 +3429,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>277</v>
+        <v>3963</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>49.9</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3470,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3525,19 +3484,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3796</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>49.9</v>
+        <v>78</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3511,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3566,19 +3525,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3446</v>
       </c>
       <c r="G31" t="n">
-        <v>78</v>
+        <v>29.9</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3547,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3603,23 +3562,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3292</v>
+        <v>1106</v>
       </c>
       <c r="G32" t="n">
-        <v>29.9</v>
+        <v>58</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3593,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3648,19 +3607,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1102</v>
+        <v>203</v>
       </c>
       <c r="G33" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3675,33 +3634,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>197</v>
+        <v>505</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3716,33 +3675,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>488</v>
+        <v>4338</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3752,38 +3711,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4330</v>
-      </c>
-      <c r="G36" t="n">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3798,35 +3759,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>73</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>320</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -3836,38 +3795,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>267</v>
+        <v>422</v>
       </c>
       <c r="G38" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -3882,33 +3841,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3918,38 +3877,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>247</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>280</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -3959,77 +3918,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G41" t="n">
-        <v>280</v>
+        <v>680</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>24</v>
-      </c>
-      <c r="G42" t="n">
-        <v>680</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9617</v>
+        <v>9621</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
         <v>158</v>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2161</v>
+        <v>2194</v>
       </c>
       <c r="G10" t="n">
         <v>75</v>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1643</v>
+        <v>1661</v>
       </c>
       <c r="G12" t="n">
         <v>59</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2766</v>
+        <v>2789</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4120</v>
+        <v>4165</v>
       </c>
       <c r="G15" t="n">
         <v>19.9</v>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3963</v>
+        <v>4069</v>
       </c>
       <c r="G25" t="n">
         <v>49.9</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3446</v>
+        <v>3529</v>
       </c>
       <c r="G27" t="n">
-        <v>29.9</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4338</v>
+        <v>4351</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="G33" t="n">
         <v>8.800000000000001</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9617</v>
+        <v>9621</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="G11" t="n">
         <v>68</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2161</v>
+        <v>2194</v>
       </c>
       <c r="G12" t="n">
         <v>75</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1643</v>
+        <v>1661</v>
       </c>
       <c r="G14" t="n">
         <v>59</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2766</v>
+        <v>2789</v>
       </c>
       <c r="G16" t="n">
         <v>75</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G17" t="n">
         <v>70</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4121</v>
+        <v>4165</v>
       </c>
       <c r="G18" t="n">
         <v>19.9</v>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G20" t="n">
         <v>21.9</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G21" t="n">
         <v>48</v>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="G22" t="n">
         <v>55</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G23" t="n">
         <v>65</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G27" t="n">
         <v>93</v>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3963</v>
+        <v>4069</v>
       </c>
       <c r="G29" t="n">
         <v>49.9</v>
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3446</v>
+        <v>3529</v>
       </c>
       <c r="G31" t="n">
-        <v>29.9</v>
+        <v>70</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1106</v>
+        <v>1111</v>
       </c>
       <c r="G32" t="n">
         <v>58</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4338</v>
+        <v>4351</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -3730,7 +3730,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="G39" t="n">
         <v>8.800000000000001</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G41" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -564,40 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·原神x穹铁北京同人嘉年华6th</t>
+          <t>北京·跨次元派对2.0童话奇妙夜</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>844</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>158</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -607,40 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·国乙同好嘉年华5th</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>506</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>730</v>
+      </c>
+      <c r="G5" t="n">
+        <v>68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -650,40 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2252</v>
+      </c>
+      <c r="G6" t="n">
+        <v>75</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80922</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -693,40 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9621</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="G7" t="n">
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -736,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>1691</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -777,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>722</v>
+        <v>2849</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -818,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2194</v>
+        <v>154</v>
       </c>
       <c r="G10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -859,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>4237</v>
       </c>
       <c r="G11" t="n">
-        <v>158</v>
+        <v>19.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -900,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1661</v>
+        <v>360</v>
       </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -941,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2789</v>
+        <v>189</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>21.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -982,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G14" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -1023,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4165</v>
+        <v>541</v>
       </c>
       <c r="G15" t="n">
-        <v>19.9</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -1064,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>352</v>
+        <v>251</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -1105,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>21.9</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1146,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>529</v>
+        <v>80</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,38 +1220,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>247</v>
+        <v>95</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,38 +1261,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>289</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1310,38 +1302,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>4113</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>49.9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1351,38 +1343,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1397,33 +1389,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>285</v>
+        <v>3599</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1433,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4069</v>
+        <v>1119</v>
       </c>
       <c r="G25" t="n">
-        <v>49.9</v>
+        <v>58</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1474,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1507,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3529</v>
+        <v>527</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1561,33 +1553,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1111</v>
+        <v>4360</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1597,38 +1589,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>203</v>
-      </c>
-      <c r="G29" t="n">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>511</v>
+        <v>431</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1679,38 +1673,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4351</v>
+        <v>489</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -1720,161 +1714,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>76</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>415</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2024-04-04</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>355</v>
-      </c>
-      <c r="G33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>440</v>
-      </c>
-      <c r="G34" t="n">
-        <v>75</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>341</v>
-      </c>
-      <c r="G35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -1964,7 +1833,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -1996,12 +1865,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -2017,7 +1886,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -2046,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>280</v>
@@ -2087,7 +1956,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2187,7 +2056,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2228,7 +2097,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2255,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,7 +2197,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2369,7 +2238,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2410,7 +2279,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2451,7 +2320,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -2473,40 +2342,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·原神x穹铁北京同人嘉年华6th</t>
+          <t>北京·跨次元派对2.0童话奇妙夜</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>844</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>43</v>
+      </c>
+      <c r="G6" t="n">
+        <v>158</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79421</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/hMaHScnn1701847387181.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -2516,40 +2383,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·国乙同好嘉年华5th</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>506</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>730</v>
+      </c>
+      <c r="G7" t="n">
+        <v>68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/udtWOaYX1699239774163.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -2559,40 +2424,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2252</v>
+      </c>
+      <c r="G8" t="n">
+        <v>75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80922</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -2602,40 +2465,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·第十四届IJOY漫展xCGF游戏节</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 09:00-01.29 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9621</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="G9" t="n">
+        <v>158</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77785</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/FJ39rv8s1698373922172.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -2645,38 +2506,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>1691</v>
       </c>
       <c r="G10" t="n">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -2686,38 +2547,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>722</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2727,38 +2588,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2194</v>
+        <v>2849</v>
       </c>
       <c r="G12" t="n">
         <v>75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -2768,38 +2629,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>154</v>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -2809,38 +2670,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1661</v>
+        <v>4237</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>19.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -2850,38 +2711,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -2891,38 +2752,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2789</v>
+        <v>189</v>
       </c>
       <c r="G16" t="n">
-        <v>75</v>
+        <v>21.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -2932,38 +2793,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -2973,38 +2834,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4165</v>
+        <v>541</v>
       </c>
       <c r="G18" t="n">
-        <v>19.9</v>
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3014,38 +2875,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>352</v>
+        <v>251</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3055,38 +2916,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>21.9</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3096,38 +2957,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3137,38 +2998,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>529</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3178,38 +3039,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3219,38 +3080,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3121,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>东郎电影创意产业园 东郎电影创意产业园</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>289</v>
       </c>
       <c r="G25" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/z5xmbhc61704790463449.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3301,38 +3162,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>80</v>
+        <v>4113</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>49.9</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3342,38 +3203,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3388,33 +3249,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>285</v>
+        <v>3599</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3424,38 +3285,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4069</v>
+        <v>1119</v>
       </c>
       <c r="G29" t="n">
-        <v>49.9</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3465,38 +3326,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="G30" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3506,38 +3367,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3529</v>
+        <v>527</v>
       </c>
       <c r="G31" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3552,33 +3413,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1111</v>
+        <v>4360</v>
       </c>
       <c r="G32" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3588,38 +3449,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>203</v>
-      </c>
-      <c r="G33" t="n">
-        <v>75</v>
+        <v>80</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3629,38 +3492,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>511</v>
+        <v>431</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -3670,38 +3533,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4351</v>
+        <v>489</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -3711,40 +3574,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>76</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>416</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3754,38 +3615,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>355</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>280</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -3795,159 +3656,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>440</v>
+        <v>27</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
+        <v>680</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>341</v>
-      </c>
-      <c r="G39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="n">
-        <v>280</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>25</v>
-      </c>
-      <c r="G41" t="n">
-        <v>680</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
         <v>158</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2252</v>
+        <v>2283</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1691</v>
+        <v>1712</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2849</v>
+        <v>2890</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4237</v>
+        <v>4301</v>
       </c>
       <c r="G11" t="n">
         <v>19.9</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G20" t="n">
         <v>93</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4113</v>
+        <v>4141</v>
       </c>
       <c r="G22" t="n">
         <v>49.9</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3599</v>
+        <v>3626</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="G25" t="n">
         <v>58</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4360</v>
+        <v>4365</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>431</v>
+        <v>481</v>
       </c>
       <c r="G30" t="n">
         <v>8.800000000000001</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>415</v>
+        <v>455</v>
       </c>
       <c r="G32" t="n">
         <v>8.800000000000001</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>280</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
         <v>158</v>
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="G7" t="n">
         <v>68</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2252</v>
+        <v>2283</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1691</v>
+        <v>1712</v>
       </c>
       <c r="G10" t="n">
         <v>59</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2849</v>
+        <v>2890</v>
       </c>
       <c r="G12" t="n">
         <v>75</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G13" t="n">
         <v>70</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4237</v>
+        <v>4302</v>
       </c>
       <c r="G14" t="n">
         <v>19.9</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G16" t="n">
         <v>21.9</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="G18" t="n">
         <v>55</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
         <v>88</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G24" t="n">
         <v>93</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4113</v>
+        <v>4141</v>
       </c>
       <c r="G26" t="n">
         <v>49.9</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3599</v>
+        <v>3626</v>
       </c>
       <c r="G28" t="n">
         <v>70</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4360</v>
+        <v>4365</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>431</v>
+        <v>481</v>
       </c>
       <c r="G34" t="n">
         <v>8.800000000000001</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>416</v>
+        <v>455</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>280</v>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G38" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·跨次元派对2.0童话奇妙夜（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -583,10 +583,12 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
-      </c>
-      <c r="G4" t="n">
-        <v>158</v>
+        <v>49</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -665,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2283</v>
+        <v>2332</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -706,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -747,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1712</v>
+        <v>1736</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -788,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2890</v>
+        <v>2929</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -829,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -870,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4301</v>
+        <v>4385</v>
       </c>
       <c r="G11" t="n">
         <v>19.9</v>
@@ -911,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -993,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1034,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1075,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1116,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1157,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1198,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1239,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
         <v>93</v>
@@ -1280,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1321,10 +1323,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4141</v>
+        <v>4398</v>
       </c>
       <c r="G22" t="n">
-        <v>49.9</v>
+        <v>70.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1403,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3626</v>
+        <v>3650</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -1444,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="G25" t="n">
         <v>58</v>
@@ -1485,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1526,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1567,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4365</v>
+        <v>4369</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1608,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1651,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>481</v>
+        <v>551</v>
       </c>
       <c r="G30" t="n">
         <v>8.800000000000001</v>
@@ -1692,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1733,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>455</v>
+        <v>511</v>
       </c>
       <c r="G32" t="n">
         <v>8.800000000000001</v>
@@ -1833,7 +1835,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -1874,7 +1876,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -1956,7 +1958,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -1983,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2056,7 +2058,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2097,7 +2099,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2110,6 +2112,47 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/yf8VthSg1703498739957.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-01-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>北京·哈利波特主题限时店-comefor“魔法世界”冰雪好礼</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024.01.26 10:00-02.26 22:00</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81515</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/xxLq9CJV1706583383790.jpeg</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,7 +2240,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2279,7 +2322,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2306,12 +2349,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·我的爸爸是条龙主题快闪店——线下集章之旅</t>
+          <t>北京·哈利波特主题限时店-comefor“魔法世界”冰雪好礼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>复兴门外大街15号 长安商场</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2320,19 +2363,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81427</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81515</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/A1VDdvxs1706178337277.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/xxLq9CJV1706583383790.jpeg</t>
         </is>
       </c>
     </row>
@@ -2342,38 +2385,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜</t>
+          <t>北京·我的爸爸是条龙主题快闪店——线下集章之旅</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>复兴门外大街15号 长安商场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.01.26 10:00-02.26 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81427</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/A1VDdvxs1706178337277.jpeg</t>
         </is>
       </c>
     </row>
@@ -2383,38 +2426,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·跨次元派对2.0童话奇妙夜（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>丽泽天地购物中心 丽泽天地购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.02 20:00-02.03 02:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>735</v>
-      </c>
-      <c r="G7" t="n">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
         </is>
       </c>
     </row>
@@ -2429,33 +2474,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2283</v>
+        <v>744</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2515,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2484,19 +2529,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>2332</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -2511,33 +2556,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1712</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -2547,38 +2592,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1736</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -2588,38 +2633,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2890</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2634,33 +2679,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>163</v>
+        <v>2929</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2720,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2689,19 +2734,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4302</v>
+        <v>167</v>
       </c>
       <c r="G14" t="n">
-        <v>19.9</v>
+        <v>70</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -2711,38 +2756,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>370</v>
+        <v>4385</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>19.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -2757,33 +2802,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>194</v>
+        <v>378</v>
       </c>
       <c r="G16" t="n">
-        <v>21.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -2793,38 +2838,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>137</v>
+        <v>208</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>21.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -2839,33 +2884,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>547</v>
+        <v>139</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -2875,38 +2920,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>255</v>
+        <v>553</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -2921,33 +2966,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>262</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -2962,33 +3007,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -2998,38 +3043,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3039,38 +3084,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3085,33 +3130,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3121,38 +3166,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>296</v>
+        <v>105</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3167,33 +3212,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4141</v>
+        <v>302</v>
       </c>
       <c r="G26" t="n">
-        <v>49.9</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3253,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3222,19 +3267,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>4398</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>70.2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3294,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3263,19 +3308,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3626</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3330,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3300,23 +3345,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1127</v>
+        <v>3650</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3331,12 +3376,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3345,19 +3390,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>209</v>
+        <v>1133</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3372,33 +3417,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>535</v>
+        <v>211</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3413,33 +3458,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4365</v>
+        <v>558</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3449,40 +3494,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>83</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4369</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3497,33 +3540,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>481</v>
-      </c>
-      <c r="G34" t="n">
-        <v>8.800000000000001</v>
+        <v>86</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3533,38 +3578,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -3579,33 +3624,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>455</v>
+        <v>552</v>
       </c>
       <c r="G36" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -3615,38 +3660,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>511</v>
       </c>
       <c r="G37" t="n">
-        <v>280</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
       </c>
     </row>
@@ -3656,36 +3701,77 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.05.18 20:00-05.18 22:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>280</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>28</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F39" t="n">
+        <v>29</v>
+      </c>
+      <c r="G39" t="n">
         <v>680</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2332</v>
+        <v>2357</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1736</v>
+        <v>1753</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2929</v>
+        <v>2971</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4385</v>
+        <v>4431</v>
       </c>
       <c r="G11" t="n">
-        <v>19.9</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4398</v>
+        <v>4482</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3650</v>
+        <v>3673</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="G25" t="n">
         <v>58</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4369</v>
+        <v>4373</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>551</v>
+        <v>586</v>
       </c>
       <c r="G30" t="n">
         <v>8.800000000000001</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="G32" t="n">
         <v>8.800000000000001</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2332</v>
+        <v>2357</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1736</v>
+        <v>1754</v>
       </c>
       <c r="G11" t="n">
         <v>59</v>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2929</v>
+        <v>2971</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4385</v>
+        <v>4431</v>
       </c>
       <c r="G15" t="n">
-        <v>19.9</v>
+        <v>70</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
         <v>88</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G25" t="n">
         <v>93</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4398</v>
+        <v>4482</v>
       </c>
       <c r="G27" t="n">
         <v>70.2</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
         <v>78</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3650</v>
+        <v>3673</v>
       </c>
       <c r="G29" t="n">
         <v>70</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4369</v>
+        <v>4373</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>551</v>
+        <v>586</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>552</v>
+        <v>580</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2357</v>
+        <v>2399</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1753</v>
+        <v>1774</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2971</v>
+        <v>3019</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4431</v>
+        <v>4486</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>620</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G20" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4482</v>
+        <v>4534</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3673</v>
+        <v>4034</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="G25" t="n">
         <v>58</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4373</v>
+        <v>4380</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="G30" t="n">
         <v>8.800000000000001</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="G32" t="n">
         <v>8.800000000000001</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2357</v>
+        <v>2399</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1754</v>
+        <v>1774</v>
       </c>
       <c r="G11" t="n">
         <v>59</v>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2971</v>
+        <v>3019</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4431</v>
+        <v>4486</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>620</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
         <v>88</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G25" t="n">
         <v>93</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4482</v>
+        <v>4534</v>
       </c>
       <c r="G27" t="n">
         <v>70.2</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3673</v>
+        <v>4034</v>
       </c>
       <c r="G29" t="n">
         <v>70</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4373</v>
+        <v>4380</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G39" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2399</v>
+        <v>2417</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1774</v>
+        <v>1787</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3019</v>
+        <v>3034</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4486</v>
+        <v>4517</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G20" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4534</v>
+        <v>4553</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4034</v>
+        <v>4098</v>
       </c>
       <c r="G24" t="n">
         <v>70</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="G25" t="n">
         <v>58</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4380</v>
+        <v>4388</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>624</v>
+        <v>651</v>
       </c>
       <c r="G30" t="n">
         <v>8.800000000000001</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="G32" t="n">
         <v>8.800000000000001</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>280</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>68</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2399</v>
+        <v>2417</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1774</v>
+        <v>1787</v>
       </c>
       <c r="G11" t="n">
         <v>59</v>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3019</v>
+        <v>3034</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4486</v>
+        <v>4517</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G25" t="n">
         <v>93</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4534</v>
+        <v>4553</v>
       </c>
       <c r="G27" t="n">
         <v>70.2</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4034</v>
+        <v>4098</v>
       </c>
       <c r="G29" t="n">
         <v>70</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4380</v>
+        <v>4388</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>624</v>
+        <v>651</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
         <v>280</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G39" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2417</v>
+        <v>2448</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1787</v>
+        <v>1813</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3034</v>
+        <v>3082</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4517</v>
+        <v>4571</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>315</v>
+        <v>122</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4553</v>
+        <v>317</v>
       </c>
       <c r="G22" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1364,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>4585</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>70.2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4098</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1147</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>595</v>
+        <v>4313</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1565,23 +1565,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4388</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,40 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>95</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1153</v>
+      </c>
+      <c r="G29" t="n">
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1634,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>651</v>
+        <v>222</v>
       </c>
       <c r="G30" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1673,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,36 +1714,284 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>石景山路68号 北京首钢会展中心</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.03.23 09:00-03.24 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4387</v>
+      </c>
+      <c r="G32" t="n">
+        <v>75</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>北京·游园3.0代号鸢周年Only</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.30 17:00</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>22</v>
+      </c>
+      <c r="G33" t="n">
+        <v>88</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/kPBLx8n01706754526213.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>北京展览馆 北京展览馆</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.04.04 09:30-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>101</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.04.04 09:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>694</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>北京·Yok运动番Only</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2024.04.06 10:00-04.06 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" t="n">
+        <v>78</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>640</v>
+      </c>
+      <c r="G37" t="n">
+        <v>75</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>597</v>
-      </c>
-      <c r="G32" t="n">
+      <c r="F38" t="n">
+        <v>631</v>
+      </c>
+      <c r="G38" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -1762,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,7 +2081,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -1876,7 +2122,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -1898,38 +2144,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1939,36 +2185,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024.05.18 20:00-05.18 22:00</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>280</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>34</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G6" t="n">
         <v>680</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>
@@ -2058,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2099,7 +2386,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2140,7 +2427,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2167,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,7 +2527,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2322,7 +2609,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2363,7 +2650,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2488,7 +2775,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2529,7 +2816,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2417</v>
+        <v>2448</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2611,7 +2898,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1787</v>
+        <v>1814</v>
       </c>
       <c r="G11" t="n">
         <v>59</v>
@@ -2652,7 +2939,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>180</v>
@@ -2693,7 +2980,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3034</v>
+        <v>3082</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -2734,7 +3021,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -2775,7 +3062,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4517</v>
+        <v>4571</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -2816,7 +3103,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -2857,7 +3144,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -2898,7 +3185,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -2939,7 +3226,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -2980,7 +3267,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3021,7 +3308,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3062,7 +3349,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -3084,38 +3371,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3412,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3171,33 +3458,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="G25" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3207,38 +3494,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>315</v>
+        <v>122</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3253,33 +3540,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4553</v>
+        <v>317</v>
       </c>
       <c r="G27" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3581,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3308,19 +3595,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>4585</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>70.2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,33 +3622,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4098</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3658,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1147</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3699,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3740,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>595</v>
+        <v>4313</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3781,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3509,23 +3796,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4388</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,40 +3822,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>95</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1153</v>
+      </c>
+      <c r="G34" t="n">
+        <v>58</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3578,38 +3863,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>651</v>
+        <v>222</v>
       </c>
       <c r="G35" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3619,38 +3904,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3660,38 +3945,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>597</v>
+        <v>4387</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3701,38 +3986,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -3742,36 +4027,325 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>北京·游园3.0代号鸢周年Only</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.03.30 10:00-03.30 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>22</v>
+      </c>
+      <c r="G39" t="n">
+        <v>88</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/kPBLx8n01706754526213.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>北京展览馆 北京展览馆</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.04.04 09:30-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>101</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024-04-04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.04.04 09:00-04.05 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>694</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>北京·Yok运动番Only</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.04.06 10:00-04.06 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" t="n">
+        <v>78</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>640</v>
+      </c>
+      <c r="G43" t="n">
+        <v>75</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:00-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>631</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2024.05.18 20:00-05.18 22:00</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>280</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>34</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="F46" t="n">
+        <v>38</v>
+      </c>
+      <c r="G46" t="n">
         <v>680</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2448</v>
+        <v>2463</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1813</v>
+        <v>1829</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3082</v>
+        <v>3104</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4571</v>
+        <v>4600</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
         <v>66</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G21" t="n">
         <v>93</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4585</v>
+        <v>4599</v>
       </c>
       <c r="G23" t="n">
         <v>70.2</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>238</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
         <v>128</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4313</v>
+        <v>4731</v>
       </c>
       <c r="G27" t="n">
         <v>70</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4387</v>
+        <v>4390</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G33" t="n">
         <v>88</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G36" t="n">
         <v>78</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>631</v>
+        <v>650</v>
       </c>
       <c r="G38" t="n">
         <v>8.800000000000001</v>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2448</v>
+        <v>2463</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1814</v>
+        <v>1829</v>
       </c>
       <c r="G11" t="n">
         <v>59</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3082</v>
+        <v>3104</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4571</v>
+        <v>4600</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G22" t="n">
         <v>65</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
         <v>66</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G26" t="n">
         <v>93</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4585</v>
+        <v>4599</v>
       </c>
       <c r="G28" t="n">
         <v>70.2</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>238</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G30" t="n">
         <v>128</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4313</v>
+        <v>4731</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>128</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="G34" t="n">
         <v>58</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4387</v>
+        <v>4390</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="G43" t="n">
         <v>75</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>631</v>
+        <v>650</v>
       </c>
       <c r="G44" t="n">
         <v>8.800000000000001</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G5" t="n">
         <v>68</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2463</v>
+        <v>2486</v>
       </c>
       <c r="G6" t="n">
         <v>75</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
         <v>158</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1829</v>
+        <v>1835</v>
       </c>
       <c r="G8" t="n">
         <v>59</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3104</v>
+        <v>3155</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4600</v>
+        <v>4649</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>628</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>9.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>632</v>
       </c>
       <c r="G19" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>271</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>319</v>
+        <v>85</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4599</v>
+        <v>129</v>
       </c>
       <c r="G23" t="n">
-        <v>70.2</v>
+        <v>93</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>322</v>
       </c>
       <c r="G24" t="n">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1442,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>4632</v>
       </c>
       <c r="G25" t="n">
-        <v>128</v>
+        <v>70.2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1483,23 +1483,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1514,33 +1514,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4731</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1565,23 +1565,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1606,23 +1606,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1158</v>
+        <v>5090</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,33 +1678,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>618</v>
+        <v>1164</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1719,33 +1719,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4390</v>
+        <v>225</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·游园3.0代号鸢周年Only</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>49</v>
+        <v>634</v>
       </c>
       <c r="G33" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/kPBLx8n01706754526213.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,40 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>103</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>4395</v>
+      </c>
+      <c r="G34" t="n">
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,38 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>712</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>8.800000000000001</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1880,38 +1878,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1919,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>657</v>
-      </c>
-      <c r="G37" t="n">
-        <v>75</v>
+        <v>107</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1977,21 +1977,144 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>650</v>
+        <v>744</v>
       </c>
       <c r="G38" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>北京·Yok运动番Only</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.04.06 10:00-04.06 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>46</v>
+      </c>
+      <c r="G39" t="n">
+        <v>78</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>680</v>
+      </c>
+      <c r="G40" t="n">
+        <v>75</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:00-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>677</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -2122,7 +2245,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2163,7 +2286,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2245,7 +2368,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2345,7 +2468,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2386,7 +2509,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2427,7 +2550,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2454,7 +2577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2527,7 +2650,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2609,7 +2732,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2650,7 +2773,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2775,7 +2898,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -2816,7 +2939,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2463</v>
+        <v>2486</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2857,7 +2980,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>158</v>
@@ -2898,7 +3021,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1829</v>
+        <v>1835</v>
       </c>
       <c r="G11" t="n">
         <v>59</v>
@@ -2980,7 +3103,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3104</v>
+        <v>3155</v>
       </c>
       <c r="G13" t="n">
         <v>75</v>
@@ -3021,7 +3144,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
@@ -3062,7 +3185,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4600</v>
+        <v>4649</v>
       </c>
       <c r="G15" t="n">
         <v>70</v>
@@ -3103,7 +3226,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3144,7 +3267,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G17" t="n">
         <v>21.9</v>
@@ -3185,7 +3308,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G18" t="n">
         <v>48</v>
@@ -3226,7 +3349,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -3267,7 +3390,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3294,33 +3417,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>628</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,33 +3458,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>260</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>65</v>
+        <v>9.9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3376,33 +3499,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>632</v>
       </c>
       <c r="G23" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3535,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>271</v>
       </c>
       <c r="G24" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3576,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3617,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3658,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>319</v>
+        <v>85</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3699,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4599</v>
+        <v>129</v>
       </c>
       <c r="G28" t="n">
-        <v>70.2</v>
+        <v>93</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3622,33 +3745,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>322</v>
       </c>
       <c r="G29" t="n">
-        <v>238</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3786,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3673,23 +3796,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>4632</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>70.2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3827,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3714,23 +3837,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G31" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,33 +3868,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4731</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3904,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3796,23 +3919,23 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3945,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3837,23 +3960,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1158</v>
+        <v>5090</v>
       </c>
       <c r="G34" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3986,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3909,33 +4032,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>618</v>
+        <v>1164</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,33 +4073,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4390</v>
+        <v>225</v>
       </c>
       <c r="G37" t="n">
         <v>75</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +4109,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>634</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +4150,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·游园3.0代号鸢周年Only</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>49</v>
+        <v>4395</v>
       </c>
       <c r="G39" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/kPBLx8n01706754526213.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,40 +4191,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>103</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>68</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4111,38 +4232,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>712</v>
+        <v>7</v>
       </c>
       <c r="G41" t="n">
-        <v>8.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4273,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4314,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>656</v>
-      </c>
-      <c r="G43" t="n">
-        <v>75</v>
+        <v>107</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,12 +4357,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4249,23 +4372,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>650</v>
+        <v>744</v>
       </c>
       <c r="G44" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4398,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G45" t="n">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,36 +4439,159 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>680</v>
+      </c>
+      <c r="G46" t="n">
+        <v>75</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:00-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>677</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.05.18 20:00-05.18 22:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>280</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>38</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="F49" t="n">
+        <v>40</v>
+      </c>
+      <c r="G49" t="n">
         <v>680</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -564,40 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜（取消）</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>770</v>
+      </c>
+      <c r="G4" t="n">
+        <v>78</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -612,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>767</v>
+        <v>2497</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -653,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -667,19 +665,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2486</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>1849</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -730,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1835</v>
+        <v>3175</v>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3155</v>
+        <v>196</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,7 +815,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -831,19 +829,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>195</v>
+        <v>4668</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4649</v>
+        <v>433</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -899,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>429</v>
+        <v>255</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="G13" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>144</v>
+        <v>600</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>594</v>
+        <v>280</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1061,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>279</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1102,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1143,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1159,19 +1157,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>633</v>
       </c>
       <c r="G18" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1184,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>632</v>
+        <v>275</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1261,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1307,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1343,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>129</v>
+        <v>324</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1389,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>322</v>
+        <v>4651</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1430,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1440,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4632</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1471,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1487,19 +1485,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1512,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1524,23 +1522,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1553,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1569,19 +1567,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>5492</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1589,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5090</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>1168</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1676,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1692,19 +1690,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1164</v>
+        <v>230</v>
       </c>
       <c r="G31" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1719,33 +1717,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>225</v>
+        <v>640</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1760,33 +1758,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>634</v>
+        <v>4398</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1794,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4395</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1835,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G35" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1878,38 +1876,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
-      </c>
-      <c r="G36" t="n">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1924,35 +1924,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>107</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>762</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1960,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>744</v>
+        <v>48</v>
       </c>
       <c r="G38" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,38 +2001,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>699</v>
       </c>
       <c r="G39" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2049,72 +2047,31 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="G40" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>677</v>
-      </c>
-      <c r="G41" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -2245,7 +2202,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2330,7 +2287,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2368,7 +2325,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2468,7 +2425,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2509,7 +2466,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2550,7 +2507,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2577,7 +2534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2650,7 +2607,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2691,7 +2648,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2732,7 +2689,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2773,7 +2730,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2836,40 +2793,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·跨次元派对2.0童话奇妙夜（取消）</t>
+          <t>北京·EXA·孤独摇滚ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>丽泽天地购物中心 丽泽天地购物中心</t>
+          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.02 20:00-02.03 02:00</t>
+          <t>2024.02.03 09:30-02.03 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>770</v>
+      </c>
+      <c r="G7" t="n">
+        <v>78</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81223</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/9MnYlQSm1705910360651.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
         </is>
       </c>
     </row>
@@ -2884,33 +2839,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·万游引力x云果 二次元新春大聚会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.03 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>767</v>
+        <v>2497</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2880,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2939,19 +2894,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2486</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
         </is>
       </c>
     </row>
@@ -2966,33 +2921,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>1849</v>
       </c>
       <c r="G10" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -3002,38 +2957,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1835</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -3043,38 +2998,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>3175</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -3089,33 +3044,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3155</v>
+        <v>196</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3085,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3144,19 +3099,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>195</v>
+        <v>4668</v>
       </c>
       <c r="G14" t="n">
         <v>70</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3121,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4649</v>
+        <v>433</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3212,33 +3167,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>429</v>
+        <v>255</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3248,38 +3203,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="G17" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3294,33 +3249,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>144</v>
+        <v>600</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3285,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>594</v>
+        <v>280</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3376,33 +3331,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>279</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3417,33 +3372,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3413,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3472,19 +3427,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>633</v>
       </c>
       <c r="G22" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3499,33 +3454,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>632</v>
+        <v>275</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,33 +3495,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3531,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3572,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="G26" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,33 +3618,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3654,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>129</v>
+        <v>324</v>
       </c>
       <c r="G28" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,33 +3700,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>322</v>
+        <v>4651</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3741,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3796,23 +3751,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4632</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3782,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3841,19 +3796,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3823,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3878,23 +3833,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3864,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3923,19 +3878,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>5493</v>
       </c>
       <c r="G33" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3900,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5090</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3941,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>1168</v>
       </c>
       <c r="G35" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -4032,12 +3987,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4046,19 +4001,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1164</v>
+        <v>230</v>
       </c>
       <c r="G36" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -4073,33 +4028,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>225</v>
+        <v>640</v>
       </c>
       <c r="G37" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4114,33 +4069,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>634</v>
+        <v>4398</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4150,38 +4105,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4395</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4191,38 +4146,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4232,38 +4187,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4273,38 +4228,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
-      </c>
-      <c r="G42" t="n">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4319,35 +4276,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>107</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>762</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4312,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>744</v>
+        <v>48</v>
       </c>
       <c r="G44" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4398,38 +4353,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>699</v>
       </c>
       <c r="G45" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4444,33 +4399,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="G46" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
       </c>
     </row>
@@ -4480,38 +4435,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>677</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
-        <v>8.800000000000001</v>
+        <v>380</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4521,77 +4476,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="G48" t="n">
-        <v>280</v>
+        <v>680</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>40</v>
-      </c>
-      <c r="G49" t="n">
-        <v>680</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>770</v>
+        <v>1861</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2497</v>
+        <v>3226</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1849</v>
+        <v>4714</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3175</v>
+        <v>446</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>21.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4668</v>
+        <v>157</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -866,23 +866,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>433</v>
+        <v>609</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="G12" t="n">
-        <v>21.9</v>
+        <v>65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>600</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>9.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,33 +1020,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>280</v>
+        <v>641</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,33 +1061,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>279</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1112,23 +1112,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>9.9</v>
+        <v>66</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1138,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>633</v>
+        <v>85</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1179,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1220,38 +1220,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>330</v>
       </c>
       <c r="G20" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1261,38 +1261,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>85</v>
+        <v>4675</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1302,38 +1302,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>93</v>
+        <v>238</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1348,33 +1348,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>324</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4651</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>70.2</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1430,33 +1430,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>5823</v>
       </c>
       <c r="G25" t="n">
-        <v>238</v>
+        <v>63</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1481,23 +1481,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1507,38 +1507,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>1176</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1548,38 +1548,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5492</v>
+        <v>234</v>
       </c>
       <c r="G28" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1589,38 +1589,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>650</v>
       </c>
       <c r="G29" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1635,33 +1635,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1168</v>
+        <v>4406</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1671,38 +1671,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1712,38 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>640</v>
+        <v>71</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1753,38 +1753,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4398</v>
-      </c>
-      <c r="G33" t="n">
-        <v>75</v>
+        <v>114</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1794,38 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>795</v>
       </c>
       <c r="G34" t="n">
-        <v>68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1835,38 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G35" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1876,40 +1878,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>111</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>725</v>
+      </c>
+      <c r="G36" t="n">
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1934,144 +1934,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>762</v>
+        <v>733</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>北京·Yok运动番Only</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>48</v>
-      </c>
-      <c r="G38" t="n">
-        <v>78</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>699</v>
-      </c>
-      <c r="G39" t="n">
-        <v>75</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>701</v>
-      </c>
-      <c r="G40" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
@@ -2202,7 +2079,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2243,7 +2120,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2284,7 +2161,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
         <v>380</v>
@@ -2325,7 +2202,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2425,7 +2302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2466,7 +2343,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2507,7 +2384,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2534,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2607,7 +2484,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2689,7 +2566,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2730,7 +2607,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2798,33 +2675,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·EXA·孤独摇滚ONLY</t>
+          <t>北京·维度*次元潮流联动展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>西三旗桥北路西88号 北京工美蓝孔雀商务酒店</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 09:30-02.03 16:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>770</v>
+        <v>1861</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77799</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202310/xzJ6MDcA1698377272373.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
         </is>
       </c>
     </row>
@@ -2834,38 +2711,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果 二次元新春大聚会</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2497</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79320</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/1qf49H3Z1705478372751.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2875,38 +2752,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·万游引力x云果次元新春狂欢节  知名配音演员 刘照坤 专场见面会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>嘉创二路6号 JDG英特尔电子竞技中心</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.03 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>3226</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/cKY6yABz1704793484477.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -2916,38 +2793,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1849</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -2957,38 +2834,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4714</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -2998,38 +2875,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3175</v>
+        <v>446</v>
       </c>
       <c r="G12" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3039,38 +2916,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>21.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3080,38 +2957,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4668</v>
+        <v>157</v>
       </c>
       <c r="G14" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3121,12 +2998,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3136,23 +3013,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>433</v>
+        <v>609</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3162,38 +3039,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="G16" t="n">
-        <v>21.9</v>
+        <v>65</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3203,38 +3080,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3244,38 +3121,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>600</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>55</v>
+        <v>9.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3290,33 +3167,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>280</v>
+        <v>641</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3331,33 +3208,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>279</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3249,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3382,23 +3259,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>9.9</v>
+        <v>66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3408,38 +3285,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>633</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3449,38 +3326,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="G23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3490,38 +3367,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="G24" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3531,38 +3408,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>330</v>
       </c>
       <c r="G25" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3572,38 +3449,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>85</v>
+        <v>4675</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3613,38 +3490,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
-        <v>93</v>
+        <v>238</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3659,33 +3536,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>324</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3577,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3714,19 +3591,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4651</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>70.2</v>
+        <v>78</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3741,33 +3618,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>5823</v>
       </c>
       <c r="G30" t="n">
-        <v>238</v>
+        <v>63</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3654,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3792,23 +3669,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
         <v>128</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3818,38 +3695,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>1176</v>
       </c>
       <c r="G32" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3859,38 +3736,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5493</v>
+        <v>234</v>
       </c>
       <c r="G33" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3900,38 +3777,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>650</v>
       </c>
       <c r="G34" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3946,33 +3823,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1168</v>
+        <v>4406</v>
       </c>
       <c r="G35" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3982,38 +3859,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4023,38 +3900,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>640</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4064,38 +3941,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4398</v>
+        <v>71</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4105,38 +3982,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>68</v>
+        <v>114</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4146,38 +4025,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>795</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4187,38 +4066,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G41" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4228,40 +4107,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>111</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>725</v>
+      </c>
+      <c r="G42" t="n">
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4148,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4286,23 +4163,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.05.01 09:00-05.03 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>762</v>
+        <v>733</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
         </is>
       </c>
     </row>
@@ -4312,38 +4189,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4353,159 +4230,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>699</v>
+        <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>75</v>
+        <v>680</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>701</v>
-      </c>
-      <c r="G46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" t="n">
-        <v>380</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>42</v>
-      </c>
-      <c r="G48" t="n">
-        <v>680</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="G4" t="n">
         <v>69</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3226</v>
+        <v>3251</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4714</v>
+        <v>4739</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G16" t="n">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4675</v>
+        <v>4696</v>
       </c>
       <c r="G21" t="n">
         <v>70.2</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
         <v>128</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5823</v>
+        <v>5844</v>
       </c>
       <c r="G25" t="n">
         <v>63</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4406</v>
+        <v>4409</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G32" t="n">
         <v>88</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="G34" t="n">
         <v>8.800000000000001</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1861</v>
+        <v>1866</v>
       </c>
       <c r="G7" t="n">
         <v>69</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3226</v>
+        <v>3251</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4714</v>
+        <v>4739</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
         <v>30</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G20" t="n">
         <v>65</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G24" t="n">
         <v>93</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4675</v>
+        <v>4696</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
         <v>78</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5823</v>
+        <v>5844</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="G32" t="n">
         <v>58</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4406</v>
+        <v>4409</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>68</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G38" t="n">
         <v>88</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>795</v>
+        <v>816</v>
       </c>
       <c r="G40" t="n">
         <v>8.800000000000001</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G41" t="n">
         <v>78</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1866</v>
+        <v>3287</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3251</v>
+        <v>207</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>200</v>
+        <v>4788</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4739</v>
+        <v>457</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>449</v>
+        <v>289</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="G9" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>158</v>
+        <v>621</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>615</v>
+        <v>281</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>648</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,33 +1020,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>643</v>
+        <v>285</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,33 +1061,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="G17" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1179,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>138</v>
+        <v>336</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>332</v>
+        <v>4726</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1276,23 +1276,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4696</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1358,23 +1358,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>5867</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1425,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5844</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>1190</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1183</v>
+        <v>237</v>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -1553,33 +1553,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>236</v>
+        <v>660</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1594,33 +1594,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>653</v>
+        <v>4412</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1630,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4409</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1671,38 +1671,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="G31" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1712,38 +1712,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>75</v>
-      </c>
-      <c r="G32" t="n">
-        <v>88</v>
+        <v>121</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1758,35 +1760,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>117</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>841</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>816</v>
+        <v>67</v>
       </c>
       <c r="G34" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>740</v>
+        <v>764</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1077</v>
+        <v>1087</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>68</v>
@@ -2670,38 +2670,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·维度*次元潮流联动展</t>
+          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.08 19:30-02.08 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1866</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80852</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/HSCMUu4p1705309498547.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
         </is>
       </c>
     </row>
@@ -2711,38 +2711,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·ICOS SP漫展03x五只猫</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>3287</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
         </is>
       </c>
     </row>
@@ -2757,33 +2757,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3251</v>
+        <v>207</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2812,19 +2812,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>200</v>
+        <v>4788</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -2834,38 +2834,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4739</v>
+        <v>457</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -2880,33 +2880,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>449</v>
+        <v>289</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -2916,38 +2916,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="G13" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -2962,33 +2962,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>158</v>
+        <v>621</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -2998,38 +2998,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>615</v>
+        <v>281</v>
       </c>
       <c r="G15" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3044,33 +3044,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3085,33 +3085,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3140,19 +3140,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>648</v>
       </c>
       <c r="G18" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3167,33 +3167,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>643</v>
+        <v>285</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3208,33 +3208,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3244,38 +3244,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3285,38 +3285,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3331,33 +3331,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3367,38 +3367,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>138</v>
+        <v>336</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3413,33 +3413,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>332</v>
+        <v>4726</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3464,23 +3464,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4696</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3509,19 +3509,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3546,23 +3546,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3591,19 +3591,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>5867</v>
       </c>
       <c r="G29" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3613,38 +3613,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5844</v>
+        <v>14</v>
       </c>
       <c r="G30" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3654,38 +3654,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>1190</v>
       </c>
       <c r="G31" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1183</v>
+        <v>237</v>
       </c>
       <c r="G32" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
         </is>
       </c>
     </row>
@@ -3741,33 +3741,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>236</v>
+        <v>660</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3782,33 +3782,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>653</v>
+        <v>4412</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3818,38 +3818,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4409</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -3859,38 +3859,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -3900,38 +3900,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -3941,38 +3941,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>75</v>
-      </c>
-      <c r="G38" t="n">
-        <v>88</v>
+        <v>121</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3987,35 +3989,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>117</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>841</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4025,38 +4025,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>816</v>
+        <v>67</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4066,38 +4066,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>740</v>
+        <v>764</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·第十六届IJOY漫展xCGF游戏节</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>760</v>
+        <v>801</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/khTgDsd31705893623652.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G45" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3287</v>
+        <v>3313</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4788</v>
+        <v>4810</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G8" t="n">
         <v>21.9</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>9.9</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G15" t="n">
         <v>85</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
         <v>66</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G18" t="n">
         <v>93</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4726</v>
+        <v>4744</v>
       </c>
       <c r="G20" t="n">
         <v>70.2</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
         <v>238</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5867</v>
+        <v>5881</v>
       </c>
       <c r="G24" t="n">
         <v>63</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
         <v>128</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="G26" t="n">
         <v>58</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4412</v>
+        <v>4416</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="G33" t="n">
         <v>8.800000000000001</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G34" t="n">
         <v>78</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>764</v>
+        <v>781</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3287</v>
+        <v>3313</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4788</v>
+        <v>4810</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4726</v>
+        <v>4744</v>
       </c>
       <c r="G25" t="n">
         <v>70.2</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
         <v>238</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5867</v>
+        <v>5881</v>
       </c>
       <c r="G29" t="n">
         <v>63</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
         <v>128</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="G31" t="n">
         <v>58</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4412</v>
+        <v>4416</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
         <v>68</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G37" t="n">
         <v>88</v>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="G39" t="n">
         <v>8.800000000000001</v>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G40" t="n">
         <v>78</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
         <v>70</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>764</v>
+        <v>781</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3313</v>
+        <v>3357</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4810</v>
+        <v>4851</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="G8" t="n">
         <v>21.9</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
         <v>9.9</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G15" t="n">
         <v>85</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
         <v>66</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G18" t="n">
         <v>93</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4744</v>
+        <v>4767</v>
       </c>
       <c r="G20" t="n">
         <v>70.2</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
         <v>238</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
         <v>128</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5881</v>
+        <v>5906</v>
       </c>
       <c r="G24" t="n">
         <v>63</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
         <v>128</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="G26" t="n">
         <v>58</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G27" t="n">
         <v>75</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4416</v>
+        <v>4423</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="G33" t="n">
         <v>8.800000000000001</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G34" t="n">
         <v>78</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -1951,6 +1951,47 @@
       <c r="I37" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>北京·原神only</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>68</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2161,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2202,7 +2243,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2302,7 +2343,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2343,7 +2384,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2384,7 +2425,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2411,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,7 +2525,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2566,7 +2607,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2607,7 +2648,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2730,7 +2771,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3313</v>
+        <v>3357</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2771,7 +2812,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -2812,7 +2853,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4810</v>
+        <v>4851</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -2853,7 +2894,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2894,7 +2935,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -2935,7 +2976,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -2976,7 +3017,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3017,7 +3058,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -3058,7 +3099,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3099,7 +3140,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3140,7 +3181,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3181,7 +3222,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3222,7 +3263,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3304,7 +3345,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3345,7 +3386,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3386,7 +3427,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3427,7 +3468,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4744</v>
+        <v>4767</v>
       </c>
       <c r="G25" t="n">
         <v>70.2</v>
@@ -3468,7 +3509,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
         <v>238</v>
@@ -3509,7 +3550,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G27" t="n">
         <v>128</v>
@@ -3591,7 +3632,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5881</v>
+        <v>5906</v>
       </c>
       <c r="G29" t="n">
         <v>63</v>
@@ -3632,7 +3673,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
         <v>128</v>
@@ -3673,7 +3714,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="G31" t="n">
         <v>58</v>
@@ -3714,7 +3755,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -3755,7 +3796,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3796,7 +3837,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4416</v>
+        <v>4423</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -3878,7 +3919,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3919,7 +3960,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G37" t="n">
         <v>88</v>
@@ -3960,7 +4001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4003,7 +4044,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="G39" t="n">
         <v>8.800000000000001</v>
@@ -4044,7 +4085,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G40" t="n">
         <v>78</v>
@@ -4085,7 +4126,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>70</v>
@@ -4126,7 +4167,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4167,7 +4208,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>822</v>
+        <v>854</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>
@@ -4230,36 +4271,77 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>北京·原神only</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>68</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>45</v>
-      </c>
-      <c r="G45" t="n">
+      <c r="F46" t="n">
+        <v>46</v>
+      </c>
+      <c r="G46" t="n">
         <v>680</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3357</v>
+        <v>3378</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4851</v>
+        <v>4873</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="G8" t="n">
         <v>21.9</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G13" t="n">
         <v>9.9</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G15" t="n">
         <v>85</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G18" t="n">
         <v>93</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4767</v>
+        <v>4781</v>
       </c>
       <c r="G20" t="n">
         <v>70.2</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
         <v>238</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G22" t="n">
         <v>128</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>78</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5906</v>
+        <v>5915</v>
       </c>
       <c r="G24" t="n">
         <v>63</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" t="n">
         <v>128</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="G26" t="n">
         <v>58</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G27" t="n">
         <v>75</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4423</v>
+        <v>4428</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>68</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
         <v>88</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="G33" t="n">
         <v>8.800000000000001</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G34" t="n">
         <v>78</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>854</v>
+        <v>876</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
         <v>68</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3357</v>
+        <v>3378</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4851</v>
+        <v>4873</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4767</v>
+        <v>4781</v>
       </c>
       <c r="G25" t="n">
         <v>70.2</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
         <v>238</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G27" t="n">
         <v>128</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>78</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5906</v>
+        <v>5915</v>
       </c>
       <c r="G29" t="n">
         <v>63</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
         <v>128</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="G31" t="n">
         <v>58</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4423</v>
+        <v>4428</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>68</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
         <v>88</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="G39" t="n">
         <v>8.800000000000001</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G40" t="n">
         <v>78</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
         <v>70</v>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>854</v>
+        <v>876</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
         <v>68</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,12 +569,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·ICOS SP漫展03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3378</v>
+        <v>3419</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -595,7 +595,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4873</v>
+        <v>4920</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="G8" t="n">
         <v>21.9</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
         <v>9.9</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G15" t="n">
         <v>85</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
         <v>66</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G18" t="n">
         <v>93</v>
@@ -1179,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>349</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4781</v>
+        <v>351</v>
       </c>
       <c r="G20" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1276,23 +1276,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>4801</v>
       </c>
       <c r="G21" t="n">
-        <v>238</v>
+        <v>70.2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1358,23 +1358,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5915</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1425,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>5932</v>
       </c>
       <c r="G25" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1202</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1507,38 +1507,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1553,33 +1553,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>680</v>
+        <v>3204</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1594,33 +1594,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4428</v>
+        <v>279</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1630,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>686</v>
       </c>
       <c r="G30" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1671,38 +1671,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>100</v>
+        <v>4428</v>
       </c>
       <c r="G31" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1712,40 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>130</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>309</v>
+      </c>
+      <c r="G32" t="n">
+        <v>68</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1753,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>883</v>
+        <v>102</v>
       </c>
       <c r="G33" t="n">
-        <v>8.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1794,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>76</v>
-      </c>
-      <c r="G34" t="n">
-        <v>78</v>
+        <v>134</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>905</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1878,38 +1878,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>803</v>
+        <v>76</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1919,38 +1919,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>876</v>
+        <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1960,38 +1960,202 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>北京·次元风暴游园会</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.04.20 09:00-04.21 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>55</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:30-05.03 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>819</v>
+      </c>
+      <c r="G39" t="n">
+        <v>75</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:00-05.04 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>899</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2024-05-18</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>北京·原神only</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
         <v>68</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>北京·次元风暴游园会2.0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.05.18 09:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>55</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2243,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2120,7 +2284,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2243,7 +2407,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2384,7 +2548,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2425,7 +2589,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2452,7 +2616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2607,7 +2771,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2648,7 +2812,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2730,7 +2894,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>180</v>
@@ -2757,12 +2921,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03x五只猫</t>
+          <t>北京·ICOS SP漫展03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>北京电影学院影视文化产业创新园平房园区 北京五只猫娱乐Mall</t>
+          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2771,7 +2935,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3378</v>
+        <v>3419</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2783,7 +2947,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lhzaliY21705296699822.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2976,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -2853,7 +3017,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4873</v>
+        <v>4920</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -2894,7 +3058,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -2935,7 +3099,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -2976,7 +3140,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3017,7 +3181,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3058,7 +3222,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -3099,7 +3263,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3140,7 +3304,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3181,7 +3345,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3222,7 +3386,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3263,7 +3427,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3304,7 +3468,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3386,7 +3550,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3408,38 +3572,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>349</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3454,33 +3618,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4781</v>
+        <v>351</v>
       </c>
       <c r="G25" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3659,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3505,23 +3669,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>4801</v>
       </c>
       <c r="G26" t="n">
-        <v>238</v>
+        <v>70.2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3700,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3550,19 +3714,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3741,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3587,23 +3751,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3782,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3632,19 +3796,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5915</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3654,38 +3818,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>5932</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3695,38 +3859,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1202</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3736,38 +3900,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/LckXJoAQ1701673379772.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3782,33 +3946,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>680</v>
+        <v>3204</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3823,33 +3987,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4428</v>
+        <v>280</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3859,38 +4023,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>686</v>
       </c>
       <c r="G35" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3900,38 +4064,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>15</v>
+        <v>4428</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3941,38 +4105,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="G37" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -3982,40 +4146,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>130</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="G38" t="n">
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4025,38 +4187,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>883</v>
+        <v>102</v>
       </c>
       <c r="G39" t="n">
-        <v>8.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4066,38 +4228,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>76</v>
+        <v>905</v>
       </c>
       <c r="G40" t="n">
-        <v>78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4107,38 +4269,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4148,38 +4310,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>803</v>
+        <v>16</v>
       </c>
       <c r="G42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4189,38 +4351,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>876</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4230,38 +4392,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>9</v>
+        <v>819</v>
       </c>
       <c r="G44" t="n">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4271,38 +4433,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>899</v>
       </c>
       <c r="G45" t="n">
-        <v>68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4312,36 +4474,159 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2024.05.18 20:00-05.18 22:00</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>9</v>
+      </c>
+      <c r="G46" t="n">
+        <v>380</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>北京·原神only</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>68</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>北京·次元风暴游园会2.0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.05.18 09:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>55</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>46</v>
-      </c>
-      <c r="G46" t="n">
+      <c r="F49" t="n">
+        <v>51</v>
+      </c>
+      <c r="G49" t="n">
         <v>680</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3419</v>
+        <v>3439</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G5" t="n">
         <v>70</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4920</v>
+        <v>4948</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G8" t="n">
         <v>21.9</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G11" t="n">
         <v>65</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
         <v>9.9</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G15" t="n">
         <v>85</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
         <v>66</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G18" t="n">
         <v>93</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4801</v>
+        <v>4813</v>
       </c>
       <c r="G21" t="n">
         <v>70.2</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
         <v>238</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
         <v>128</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5932</v>
+        <v>5949</v>
       </c>
       <c r="G25" t="n">
         <v>63</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
         <v>128</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
         <v>50</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3204</v>
+        <v>3208</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4428</v>
+        <v>4432</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G32" t="n">
         <v>68</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G33" t="n">
         <v>88</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G36" t="n">
         <v>78</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
         <v>70</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="G39" t="n">
         <v>75</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="G40" t="n">
         <v>8.800000000000001</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3419</v>
+        <v>3439</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4920</v>
+        <v>4948</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G15" t="n">
         <v>65</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4801</v>
+        <v>4813</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G27" t="n">
         <v>238</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5932</v>
+        <v>5949</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G31" t="n">
         <v>128</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3204</v>
+        <v>3208</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4428</v>
+        <v>4432</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="G40" t="n">
         <v>8.800000000000001</v>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G41" t="n">
         <v>78</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G42" t="n">
         <v>70</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="G44" t="n">
         <v>75</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="G45" t="n">
         <v>8.800000000000001</v>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G49" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3439</v>
+        <v>3471</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·ICOS SP漫展03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>233</v>
+        <v>3471</v>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4948</v>
+        <v>243</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>493</v>
+        <v>4998</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>324</v>
+        <v>502</v>
       </c>
       <c r="G8" t="n">
-        <v>21.9</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>184</v>
+        <v>331</v>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>21.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>655</v>
+        <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>290</v>
+        <v>666</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G12" t="n">
-        <v>30</v>
+        <v>290</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -938,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>9.9</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,12 +981,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -993,19 +995,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>679</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>9.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -1020,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>298</v>
+        <v>684</v>
       </c>
       <c r="G15" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>297</v>
       </c>
       <c r="G16" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1097,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1184,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1220,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>352</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,33 +1268,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4813</v>
+        <v>357</v>
       </c>
       <c r="G21" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1309,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1317,23 +1319,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>4846</v>
       </c>
       <c r="G22" t="n">
-        <v>238</v>
+        <v>70.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1362,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1399,23 +1401,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1432,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1444,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5949</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>5969</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1514,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1526,19 +1528,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1548,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3208</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1596,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1608,19 +1610,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>295</v>
+        <v>3209</v>
       </c>
       <c r="G29" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1635,33 +1637,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>690</v>
+        <v>306</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1676,33 +1678,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4432</v>
+        <v>693</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1712,38 +1714,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>311</v>
+        <v>4436</v>
       </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1753,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>106</v>
+        <v>314</v>
       </c>
       <c r="G33" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1794,40 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>137</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>110</v>
+      </c>
+      <c r="G34" t="n">
+        <v>88</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1842,33 +1842,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>920</v>
-      </c>
-      <c r="G35" t="n">
-        <v>8.800000000000001</v>
+        <v>137</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1878,38 +1880,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
+        <v>953</v>
       </c>
       <c r="G36" t="n">
-        <v>78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1919,38 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G37" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1960,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -2001,38 +2003,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>829</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -2047,33 +2049,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>913</v>
+        <v>841</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2083,38 +2085,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>935</v>
       </c>
       <c r="G41" t="n">
-        <v>68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -2129,31 +2131,72 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>北京·原神only</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G42" t="n">
+        <v>68</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G43" t="n">
         <v>55</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2243,7 +2286,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2284,7 +2327,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2325,7 +2368,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2366,7 +2409,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>380</v>
@@ -2407,7 +2450,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
         <v>680</v>
@@ -2507,7 +2550,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2548,7 +2591,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2589,7 +2632,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2616,7 +2659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2689,7 +2732,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2730,7 +2773,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2771,7 +2814,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2812,7 +2855,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2853,7 +2896,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
         <v>68</v>
@@ -2894,7 +2937,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>180</v>
@@ -2935,7 +2978,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3439</v>
+        <v>3471</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2962,33 +3005,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·ICOS SP漫展03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>233</v>
+        <v>3471</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3046,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3017,19 +3060,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4948</v>
+        <v>243</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3039,38 +3082,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>493</v>
+        <v>4998</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3085,33 +3128,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>324</v>
+        <v>502</v>
       </c>
       <c r="G12" t="n">
-        <v>21.9</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3121,38 +3164,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>184</v>
+        <v>331</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>21.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3167,33 +3210,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>655</v>
+        <v>190</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3203,38 +3246,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>290</v>
+        <v>666</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3306,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3316,7 +3359,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/ilck1LZF1706759361504.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3388,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3386,7 +3429,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3427,7 +3470,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3468,7 +3511,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3550,7 +3593,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3632,7 +3675,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3673,7 +3716,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4813</v>
+        <v>4846</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3714,7 +3757,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
         <v>238</v>
@@ -3837,7 +3880,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5949</v>
+        <v>5969</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3919,7 +3962,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3960,7 +4003,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4001,7 +4044,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4042,7 +4085,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4083,7 +4126,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4432</v>
+        <v>4436</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4124,7 +4167,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -4165,7 +4208,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4206,7 +4249,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4233,33 +4276,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>920</v>
-      </c>
-      <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>137</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4269,38 +4314,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>77</v>
+        <v>953</v>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4310,38 +4355,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4351,38 +4396,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4392,38 +4437,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>829</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4438,33 +4483,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>913</v>
+        <v>841</v>
       </c>
       <c r="G45" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4474,38 +4519,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>935</v>
       </c>
       <c r="G46" t="n">
-        <v>380</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4520,33 +4565,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4561,33 +4606,33 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·原神only</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G48" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4597,36 +4642,77 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>北京·次元风暴游园会2.0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2024.05.18 09:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>55</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>52</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="F50" t="n">
+        <v>53</v>
+      </c>
+      <c r="G50" t="n">
         <v>680</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3471</v>
+        <v>3491</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3471</v>
+        <v>3491</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4998</v>
+        <v>5021</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4846</v>
+        <v>4866</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
         <v>238</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
         <v>128</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5969</v>
+        <v>5983</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3209</v>
+        <v>3212</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4436</v>
+        <v>4438</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3471</v>
+        <v>3491</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3471</v>
+        <v>3491</v>
       </c>
       <c r="G9" t="n">
         <v>75</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4998</v>
+        <v>5021</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4846</v>
+        <v>4866</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G27" t="n">
         <v>238</v>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5969</v>
+        <v>5983</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -4003,7 +4003,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3209</v>
+        <v>3212</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4436</v>
+        <v>4438</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4208,7 +4208,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3491</v>
+        <v>3530</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3491</v>
+        <v>3530</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5021</v>
+        <v>5056</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>58</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4866</v>
+        <v>4886</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5983</v>
+        <v>6003</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
         <v>50</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3212</v>
+        <v>3217</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4438</v>
+        <v>4440</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G33" t="n">
         <v>68</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>966</v>
+        <v>991</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2288,8 +2288,10 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="n">
-        <v>180</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2327,7 +2329,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2368,7 +2370,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -2550,7 +2552,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2591,7 +2593,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2632,7 +2634,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2732,7 +2734,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2773,7 +2775,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2814,7 +2816,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2855,7 +2857,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2939,8 +2941,10 @@
       <c r="F7" t="n">
         <v>8</v>
       </c>
-      <c r="G7" t="n">
-        <v>180</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2978,10 +2982,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3491</v>
+        <v>3530</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3019,10 +3023,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3491</v>
+        <v>3530</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>67.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3060,7 +3064,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3101,7 +3105,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5021</v>
+        <v>5056</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -3142,7 +3146,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -3183,7 +3187,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -3224,7 +3228,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3265,7 +3269,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3306,7 +3310,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3347,7 +3351,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3388,7 +3392,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3429,7 +3433,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3470,7 +3474,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3511,7 +3515,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3593,7 +3597,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3634,7 +3638,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>58</v>
@@ -3675,7 +3679,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3716,7 +3720,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4866</v>
+        <v>4886</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3880,7 +3884,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5983</v>
+        <v>6003</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3962,7 +3966,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -4003,7 +4007,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3212</v>
+        <v>3217</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4044,7 +4048,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4085,7 +4089,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4126,7 +4130,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4438</v>
+        <v>4440</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4167,7 +4171,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -4208,7 +4212,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4249,7 +4253,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4290,7 +4294,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4333,7 +4337,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>966</v>
+        <v>991</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4374,7 +4378,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4497,7 +4501,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4538,7 +4542,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4620,7 +4624,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3530</v>
+        <v>3545</v>
       </c>
       <c r="G4" t="n">
         <v>67.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3530</v>
+        <v>3545</v>
       </c>
       <c r="G5" t="n">
         <v>67.5</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5056</v>
+        <v>5065</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>510</v>
+        <v>5065</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>345</v>
+        <v>515</v>
       </c>
       <c r="G9" t="n">
-        <v>21.9</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>193</v>
+        <v>350</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>21.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>681</v>
+        <v>194</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,40 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>291</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>688</v>
+      </c>
+      <c r="G12" t="n">
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,33 +938,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
-      </c>
-      <c r="G13" t="n">
-        <v>30</v>
+        <v>291</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -981,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9</v>
+        <v>30</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>689</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>308</v>
+        <v>691</v>
       </c>
       <c r="G16" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>312</v>
       </c>
       <c r="G17" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>359</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4886</v>
+        <v>361</v>
       </c>
       <c r="G22" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>4893</v>
       </c>
       <c r="G23" t="n">
-        <v>238</v>
+        <v>70.2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>4893</v>
       </c>
       <c r="G24" t="n">
-        <v>128</v>
+        <v>70.2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1442,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6003</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1524,23 +1524,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>6016</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3217</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>327</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,33 +1678,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>701</v>
+        <v>3221</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1719,33 +1719,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4440</v>
+        <v>330</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>316</v>
+        <v>707</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>119</v>
+        <v>4442</v>
       </c>
       <c r="G34" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,40 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>139</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>317</v>
+      </c>
+      <c r="G35" t="n">
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1880,38 +1878,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>991</v>
+        <v>120</v>
       </c>
       <c r="G36" t="n">
-        <v>8.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1919,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>81</v>
-      </c>
-      <c r="G37" t="n">
-        <v>78</v>
+        <v>139</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>21</v>
+        <v>1001</v>
       </c>
       <c r="G38" t="n">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="G39" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2044,38 +2044,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>855</v>
+        <v>23</v>
       </c>
       <c r="G40" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -2085,38 +2085,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>960</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -2126,38 +2126,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>864</v>
       </c>
       <c r="G42" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2167,36 +2167,118 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>北京国家会议中心 北京国家会议中心</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.05.01 09:00-05.04 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>969</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>2024-05-18</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>北京·原神only</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G44" t="n">
+        <v>68</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G45" t="n">
         <v>55</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2213,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,40 +2349,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="G2" t="n">
+        <v>88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -2310,38 +2390,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -2351,38 +2431,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -2392,77 +2472,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>53</v>
-      </c>
-      <c r="G6" t="n">
-        <v>680</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>
@@ -2552,7 +2591,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2593,7 +2632,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2661,7 +2700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2734,7 +2773,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2816,7 +2855,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2920,40 +2959,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·【7折】拉德斯基进行曲—— 维也纳之声“金山爱乐乐团”2024新春音乐会</t>
+          <t>北京·ICOS SP漫展03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>西城区北新华街1号北京音乐厅 北京音乐厅</t>
+          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.08 19:30-02.08 21:00</t>
+          <t>2024.02.13 09:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>3545</v>
+      </c>
+      <c r="G7" t="n">
+        <v>67.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80932</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/3Ges982e1705475289966.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3019,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3530</v>
+        <v>3545</v>
       </c>
       <c r="G8" t="n">
         <v>67.5</v>
@@ -3009,33 +3046,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3530</v>
+        <v>254</v>
       </c>
       <c r="G9" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3087,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3064,19 +3101,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>252</v>
+        <v>5065</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3142,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5056</v>
+        <v>5065</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -3146,7 +3183,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -3187,7 +3224,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -3228,7 +3265,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3269,7 +3306,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3296,33 +3333,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
-      </c>
-      <c r="G16" t="n">
-        <v>30</v>
+        <v>291</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3337,33 +3376,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>9.9</v>
+        <v>30</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3417,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3392,19 +3431,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>689</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>9.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -3419,33 +3458,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>308</v>
+        <v>691</v>
       </c>
       <c r="G19" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3460,33 +3499,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>312</v>
       </c>
       <c r="G20" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3496,38 +3535,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3537,38 +3576,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3583,33 +3622,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3624,33 +3663,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>157</v>
       </c>
       <c r="G24" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3660,38 +3699,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>359</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3706,33 +3745,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4886</v>
+        <v>361</v>
       </c>
       <c r="G26" t="n">
-        <v>70.2</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3786,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3757,23 +3796,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>4893</v>
       </c>
       <c r="G27" t="n">
-        <v>238</v>
+        <v>70.2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3827,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3798,23 +3837,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>4893</v>
       </c>
       <c r="G28" t="n">
-        <v>128</v>
+        <v>70.2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3868,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3839,23 +3878,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="G29" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3870,33 +3909,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6003</v>
+        <v>40</v>
       </c>
       <c r="G30" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3945,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3921,23 +3960,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3947,38 +3986,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>15</v>
+        <v>6016</v>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +4027,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3217</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +4068,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>327</v>
+        <v>15</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -4075,33 +4114,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>701</v>
+        <v>3221</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -4116,33 +4155,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4440</v>
+        <v>330</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4191,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>316</v>
+        <v>707</v>
       </c>
       <c r="G37" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4232,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>23</v>
+        <v>4442</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4273,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>119</v>
+        <v>317</v>
       </c>
       <c r="G39" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4275,40 +4314,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>139</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="G40" t="n">
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4318,38 +4355,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>991</v>
+        <v>120</v>
       </c>
       <c r="G41" t="n">
-        <v>8.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4359,38 +4396,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>81</v>
-      </c>
-      <c r="G42" t="n">
-        <v>78</v>
+        <v>139</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4400,38 +4439,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>21</v>
+        <v>1001</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4441,38 +4480,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4482,38 +4521,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>855</v>
+        <v>23</v>
       </c>
       <c r="G45" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4523,38 +4562,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>960</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4564,38 +4603,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>864</v>
       </c>
       <c r="G47" t="n">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4605,38 +4644,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>16</v>
+        <v>969</v>
       </c>
       <c r="G48" t="n">
-        <v>68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4651,33 +4690,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G49" t="n">
-        <v>55</v>
+        <v>380</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4687,36 +4726,118 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>北京·原神only</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G50" t="n">
+        <v>68</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>北京·次元风暴游园会2.0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2024.05.18 09:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>55</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>2024-05-25</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F52" t="n">
         <v>53</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G52" t="n">
         <v>680</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3545</v>
+        <v>3572</v>
       </c>
       <c r="G4" t="n">
         <v>67.5</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3545</v>
+        <v>3572</v>
       </c>
       <c r="G5" t="n">
         <v>67.5</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="G8" t="n">
         <v>70</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G10" t="n">
         <v>21.9</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
         <v>9.9</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G17" t="n">
         <v>85</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
         <v>66</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4893</v>
+        <v>4908</v>
       </c>
       <c r="G23" t="n">
         <v>70.2</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4893</v>
+        <v>4908</v>
       </c>
       <c r="G24" t="n">
         <v>70.2</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
         <v>78</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6016</v>
+        <v>6036</v>
       </c>
       <c r="G28" t="n">
         <v>63</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
         <v>128</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
         <v>50</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4442</v>
+        <v>4444</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G36" t="n">
         <v>88</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="G38" t="n">
         <v>8.800000000000001</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G42" t="n">
         <v>75</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="G44" t="n">
         <v>68</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3545</v>
+        <v>3572</v>
       </c>
       <c r="G7" t="n">
         <v>67.5</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3545</v>
+        <v>3572</v>
       </c>
       <c r="G8" t="n">
         <v>67.5</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5065</v>
+        <v>5097</v>
       </c>
       <c r="G11" t="n">
         <v>70</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="G13" t="n">
         <v>21.9</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="G15" t="n">
         <v>55</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G17" t="n">
         <v>30</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
         <v>9.9</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G20" t="n">
         <v>85</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
         <v>66</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
         <v>88</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4893</v>
+        <v>4908</v>
       </c>
       <c r="G27" t="n">
         <v>70.2</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4893</v>
+        <v>4908</v>
       </c>
       <c r="G28" t="n">
         <v>70.2</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
         <v>78</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6016</v>
+        <v>6036</v>
       </c>
       <c r="G32" t="n">
         <v>63</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" t="n">
         <v>128</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G34" t="n">
         <v>50</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4442</v>
+        <v>4444</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
         <v>60</v>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G41" t="n">
         <v>88</v>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="G43" t="n">
         <v>8.800000000000001</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G47" t="n">
         <v>75</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="G48" t="n">
         <v>8.800000000000001</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="G50" t="n">
         <v>68</v>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G52" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3572</v>
+        <v>3585</v>
       </c>
       <c r="G4" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3572</v>
+        <v>3585</v>
       </c>
       <c r="G5" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5097</v>
+        <v>5115</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5097</v>
+        <v>532</v>
       </c>
       <c r="G8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>523</v>
+        <v>361</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>357</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>200</v>
+        <v>693</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>691</v>
-      </c>
-      <c r="G12" t="n">
-        <v>55</v>
+        <v>291</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -938,35 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>291</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>95</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>701</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>697</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>315</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,33 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>362</v>
       </c>
       <c r="G21" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>362</v>
+        <v>4917</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4908</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4908</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>70.2</v>
+        <v>128</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1442,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>6045</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1524,23 +1524,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6036</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>3222</v>
       </c>
       <c r="G29" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>343</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,33 +1678,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3221</v>
+        <v>713</v>
       </c>
       <c r="G31" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1719,33 +1719,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>342</v>
+        <v>4445</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>711</v>
+        <v>319</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4444</v>
+        <v>123</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1837,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>317</v>
-      </c>
-      <c r="G35" t="n">
-        <v>68</v>
+        <v>140</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1878,38 +1880,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>122</v>
+        <v>1026</v>
       </c>
       <c r="G36" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1919,40 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>140</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="G37" t="n">
+        <v>78</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1016</v>
+        <v>24</v>
       </c>
       <c r="G38" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -2044,38 +2044,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>874</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2085,38 +2085,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -2126,38 +2126,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·原神only</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>871</v>
+        <v>2030</v>
       </c>
       <c r="G42" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -2167,118 +2167,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>987</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>北京·原神only</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>北花园路1号 超级蜂巢</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>2027</v>
-      </c>
-      <c r="G44" t="n">
-        <v>68</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>55</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2450,7 +2368,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2591,7 +2509,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2632,7 +2550,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2700,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,7 +2691,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2855,7 +2773,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2978,10 +2896,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3572</v>
+        <v>3585</v>
       </c>
       <c r="G7" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3019,10 +2937,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3572</v>
+        <v>3585</v>
       </c>
       <c r="G8" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3060,7 +2978,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3101,7 +3019,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5097</v>
+        <v>5115</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3123,38 +3041,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5097</v>
+        <v>532</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3169,33 +3087,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>523</v>
+        <v>361</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3205,38 +3123,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>357</v>
+        <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3251,33 +3169,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>200</v>
+        <v>693</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3287,38 +3205,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>691</v>
-      </c>
-      <c r="G15" t="n">
-        <v>55</v>
+        <v>291</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3333,35 +3253,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>291</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>95</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3376,33 +3294,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3335,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3431,19 +3349,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>701</v>
       </c>
       <c r="G18" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3458,33 +3376,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>697</v>
+        <v>317</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3499,33 +3417,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>315</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3453,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3494,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3622,33 +3540,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,33 +3581,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3617,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>362</v>
       </c>
       <c r="G25" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,33 +3663,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>362</v>
+        <v>4917</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3704,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3796,23 +3714,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4908</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3745,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3837,23 +3755,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4908</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>70.2</v>
+        <v>128</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3786,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3878,23 +3796,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3909,33 +3827,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>6045</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3863,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3960,23 +3878,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3904,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6036</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +3945,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>3222</v>
       </c>
       <c r="G33" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,38 +3986,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>16</v>
+        <v>343</v>
       </c>
       <c r="G34" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -4114,33 +4032,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3221</v>
+        <v>713</v>
       </c>
       <c r="G35" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4155,33 +4073,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>342</v>
+        <v>4445</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4191,38 +4109,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>711</v>
+        <v>319</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4232,38 +4150,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4444</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4273,38 +4191,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>317</v>
+        <v>123</v>
       </c>
       <c r="G39" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4314,38 +4232,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
-      </c>
-      <c r="G40" t="n">
-        <v>60</v>
+        <v>140</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4355,38 +4275,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>122</v>
+        <v>1026</v>
       </c>
       <c r="G41" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4396,40 +4316,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>140</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="G42" t="n">
+        <v>78</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4439,38 +4357,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1016</v>
+        <v>24</v>
       </c>
       <c r="G43" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4480,38 +4398,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4521,38 +4439,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>23</v>
+        <v>874</v>
       </c>
       <c r="G45" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4562,38 +4480,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="G46" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4603,38 +4521,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>871</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4644,38 +4562,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·原神only</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>987</v>
+        <v>2030</v>
       </c>
       <c r="G48" t="n">
-        <v>8.800000000000001</v>
+        <v>68</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4690,33 +4608,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4726,118 +4644,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2027</v>
+        <v>54</v>
       </c>
       <c r="G50" t="n">
-        <v>68</v>
+        <v>680</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>55</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>54</v>
-      </c>
-      <c r="G52" t="n">
-        <v>680</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3585</v>
+        <v>3624</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3585</v>
+        <v>3624</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5115</v>
+        <v>5148</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4917</v>
+        <v>4938</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6045</v>
+        <v>6064</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" t="n">
         <v>50</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3222</v>
+        <v>3228</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4445</v>
+        <v>4446</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1026</v>
+        <v>1045</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1002</v>
+        <v>1028</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3585</v>
+        <v>3624</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3585</v>
+        <v>3624</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5115</v>
+        <v>5148</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4917</v>
+        <v>4938</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
         <v>78</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6045</v>
+        <v>6064</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3222</v>
+        <v>3228</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4445</v>
+        <v>4446</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1026</v>
+        <v>1045</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G43" t="n">
         <v>70</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1002</v>
+        <v>1028</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G47" t="n">
         <v>380</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2030</v>
+        <v>2035</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G50" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3624</v>
+        <v>3647</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3624</v>
+        <v>3647</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5148</v>
+        <v>5175</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4938</v>
+        <v>4951</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
         <v>78</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6064</v>
+        <v>6076</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3228</v>
+        <v>3233</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4446</v>
+        <v>4449</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1045</v>
+        <v>1062</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3624</v>
+        <v>3647</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3624</v>
+        <v>3647</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5148</v>
+        <v>5175</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4938</v>
+        <v>4951</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
         <v>78</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6064</v>
+        <v>6076</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3228</v>
+        <v>3233</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4446</v>
+        <v>4449</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1045</v>
+        <v>1062</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·原神only</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G50" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3647</v>
+        <v>3684</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3647</v>
+        <v>3684</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5175</v>
+        <v>5210</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4951</v>
+        <v>5968</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
         <v>238</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
         <v>128</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6076</v>
+        <v>6200</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" t="n">
         <v>128</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G28" t="n">
         <v>50</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
         <v>68</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1062</v>
+        <v>1087</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1040</v>
+        <v>1064</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3647</v>
+        <v>3684</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3647</v>
+        <v>3684</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5175</v>
+        <v>5210</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4951</v>
+        <v>5968</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
         <v>238</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6076</v>
+        <v>6200</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
         <v>128</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1062</v>
+        <v>1087</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G43" t="n">
         <v>70</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1040</v>
+        <v>1064</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G50" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3684</v>
+        <v>3699</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3684</v>
+        <v>3699</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5210</v>
+        <v>5229</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5968</v>
+        <v>5987</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
         <v>128</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6200</v>
+        <v>6298</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
         <v>50</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3238</v>
+        <v>3241</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G33" t="n">
         <v>68</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>55</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1064</v>
+        <v>1079</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3684</v>
+        <v>3699</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3684</v>
+        <v>3699</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5210</v>
+        <v>5229</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5968</v>
+        <v>5987</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6200</v>
+        <v>6298</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3238</v>
+        <v>3241</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>55</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1064</v>
+        <v>1079</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2041</v>
+        <v>2046</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3699</v>
+        <v>3725</v>
       </c>
       <c r="G4" t="n">
         <v>75</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3699</v>
+        <v>3725</v>
       </c>
       <c r="G5" t="n">
         <v>75</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G6" t="n">
         <v>70</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5229</v>
+        <v>5261</v>
       </c>
       <c r="G7" t="n">
         <v>70</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>723</v>
+        <v>1036</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5987</v>
+        <v>6017</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G24" t="n">
         <v>128</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6298</v>
+        <v>6321</v>
       </c>
       <c r="G26" t="n">
         <v>63</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
         <v>128</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
         <v>50</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3241</v>
+        <v>3250</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4449</v>
+        <v>4454</v>
       </c>
       <c r="G32" t="n">
         <v>75</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
         <v>55</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1079</v>
+        <v>1105</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2046</v>
+        <v>2052</v>
       </c>
       <c r="G42" t="n">
         <v>68</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
         <v>55</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1141</v>
+        <v>1146</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3699</v>
+        <v>3725</v>
       </c>
       <c r="G7" t="n">
         <v>75</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3699</v>
+        <v>3725</v>
       </c>
       <c r="G8" t="n">
         <v>75</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G9" t="n">
         <v>70</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5229</v>
+        <v>5261</v>
       </c>
       <c r="G10" t="n">
         <v>70</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>723</v>
+        <v>1036</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5987</v>
+        <v>6017</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6298</v>
+        <v>6321</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
         <v>128</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3241</v>
+        <v>3250</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4449</v>
+        <v>4454</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G43" t="n">
         <v>70</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
         <v>55</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1079</v>
+        <v>1105</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2046</v>
+        <v>2052</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>55</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G50" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3725</v>
+        <v>3736</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3725</v>
+        <v>3736</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         <v>290</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5261</v>
+        <v>5276</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6017</v>
+        <v>6033</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>6033</v>
       </c>
       <c r="G23" t="n">
-        <v>238</v>
+        <v>70.2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G24" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1442,23 +1442,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1487,19 +1487,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6321</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>6795</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1569,19 +1569,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3250</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1651,19 +1651,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>363</v>
+        <v>3252</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,33 +1678,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>742</v>
+        <v>364</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1719,33 +1719,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4454</v>
+        <v>745</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>322</v>
+        <v>4457</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1796,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>133</v>
+        <v>322</v>
       </c>
       <c r="G34" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1837,40 +1837,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>148</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>134</v>
+      </c>
+      <c r="G35" t="n">
+        <v>88</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1885,33 +1883,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1115</v>
-      </c>
-      <c r="G36" t="n">
-        <v>8.800000000000001</v>
+        <v>149</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>97</v>
+        <v>1129</v>
       </c>
       <c r="G37" t="n">
-        <v>78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="G38" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G39" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -2044,38 +2044,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>911</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -2090,33 +2090,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1105</v>
+        <v>916</v>
       </c>
       <c r="G41" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2126,38 +2126,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2052</v>
+        <v>1115</v>
       </c>
       <c r="G42" t="n">
-        <v>68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -2172,31 +2172,72 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>北京·原神only3.0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>北花园路1号 超级蜂巢</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2024.05.18 10:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2055</v>
+      </c>
+      <c r="G43" t="n">
+        <v>68</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="F44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" t="n">
         <v>55</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2286,7 +2327,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2409,7 +2450,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2550,7 +2591,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2591,7 +2632,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2773,7 +2814,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2814,7 +2855,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2896,10 +2937,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3725</v>
+        <v>3736</v>
       </c>
       <c r="G7" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2937,10 +2978,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3725</v>
+        <v>3736</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2981,7 +3022,7 @@
         <v>290</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3019,10 +3060,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5261</v>
+        <v>5276</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3060,7 +3101,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3101,7 +3142,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3142,7 +3183,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3183,7 +3224,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3267,7 +3308,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3308,7 +3349,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3349,7 +3390,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3390,7 +3431,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3431,7 +3472,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3472,7 +3513,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
         <v>88</v>
@@ -3636,7 +3677,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -3677,7 +3718,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6017</v>
+        <v>6033</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3841,7 +3882,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6321</v>
+        <v>6795</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3923,7 +3964,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -3964,7 +4005,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3250</v>
+        <v>3252</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4005,7 +4046,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4046,7 +4087,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4087,7 +4128,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4454</v>
+        <v>4457</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4210,7 +4251,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4251,7 +4292,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4294,7 +4335,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1115</v>
+        <v>1129</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4335,7 +4376,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4417,7 +4458,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
         <v>55</v>
@@ -4458,7 +4499,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4499,7 +4540,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1105</v>
+        <v>1115</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4581,7 +4622,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>
@@ -4622,7 +4663,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
         <v>55</v>
@@ -4663,7 +4704,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G50" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3736</v>
+        <v>3762</v>
       </c>
       <c r="G4" t="n">
         <v>85</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3736</v>
+        <v>3762</v>
       </c>
       <c r="G5" t="n">
         <v>85</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G6" t="n">
         <v>80</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5276</v>
+        <v>5301</v>
       </c>
       <c r="G7" t="n">
         <v>80</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="G9" t="n">
         <v>21.9</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1045</v>
+        <v>1062</v>
       </c>
       <c r="G11" t="n">
         <v>55</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
         <v>9.9</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="G15" t="n">
         <v>60</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="G16" t="n">
         <v>85</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
         <v>66</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6033</v>
+        <v>6068</v>
       </c>
       <c r="G22" t="n">
         <v>70.2</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6033</v>
+        <v>6068</v>
       </c>
       <c r="G23" t="n">
         <v>70.2</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
         <v>128</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
         <v>78</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6795</v>
+        <v>6826</v>
       </c>
       <c r="G27" t="n">
         <v>63</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3252</v>
+        <v>3260</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4457</v>
+        <v>4460</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G34" t="n">
         <v>68</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G35" t="n">
         <v>88</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1129</v>
+        <v>1156</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G38" t="n">
         <v>78</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G39" t="n">
         <v>70</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="G41" t="n">
         <v>75</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="G42" t="n">
         <v>8.800000000000001</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2055</v>
+        <v>2061</v>
       </c>
       <c r="G43" t="n">
         <v>68</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3736</v>
+        <v>3762</v>
       </c>
       <c r="G7" t="n">
         <v>85</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3736</v>
+        <v>3762</v>
       </c>
       <c r="G8" t="n">
         <v>85</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G9" t="n">
         <v>80</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5276</v>
+        <v>5301</v>
       </c>
       <c r="G10" t="n">
         <v>80</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="G12" t="n">
         <v>21.9</v>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1045</v>
+        <v>1062</v>
       </c>
       <c r="G14" t="n">
         <v>55</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
         <v>9.9</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="G19" t="n">
         <v>85</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G20" t="n">
         <v>66</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G23" t="n">
         <v>93</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6033</v>
+        <v>6068</v>
       </c>
       <c r="G26" t="n">
         <v>70.2</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
         <v>128</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
         <v>78</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6795</v>
+        <v>6826</v>
       </c>
       <c r="G30" t="n">
         <v>63</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
         <v>128</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G32" t="n">
         <v>50</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3252</v>
+        <v>3260</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="G34" t="n">
         <v>75</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4457</v>
+        <v>4460</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G39" t="n">
         <v>88</v>
@@ -4292,7 +4292,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1129</v>
+        <v>1156</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G42" t="n">
         <v>78</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G43" t="n">
         <v>70</v>
@@ -4499,7 +4499,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="G45" t="n">
         <v>75</v>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1115</v>
+        <v>1143</v>
       </c>
       <c r="G46" t="n">
         <v>8.800000000000001</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2055</v>
+        <v>2061</v>
       </c>
       <c r="G48" t="n">
         <v>68</v>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G50" t="n">
         <v>680</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3762</v>
+        <v>3768</v>
       </c>
       <c r="G4" t="n">
         <v>85</v>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3762</v>
+        <v>298</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>295</v>
+        <v>5315</v>
       </c>
       <c r="G6" t="n">
         <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5301</v>
+        <v>600</v>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>590</v>
+        <v>435</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>426</v>
+        <v>229</v>
       </c>
       <c r="G9" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>229</v>
+        <v>1069</v>
       </c>
       <c r="G10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -851,38 +851,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1062</v>
-      </c>
-      <c r="G11" t="n">
-        <v>55</v>
+        <v>290</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -897,35 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>290</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>146</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>735</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>731</v>
+        <v>370</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>364</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G17" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,33 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>179</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>372</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1268,33 +1268,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>370</v>
+        <v>6094</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1319,23 +1319,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6068</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6068</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>70.2</v>
+        <v>128</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,33 +1432,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>44</v>
+        <v>7038</v>
       </c>
       <c r="G25" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1483,23 +1483,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6826</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>3265</v>
       </c>
       <c r="G28" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>375</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1637,33 +1637,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3260</v>
+        <v>757</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,33 +1678,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>371</v>
+        <v>4463</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,38 +1714,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>752</v>
+        <v>325</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4460</v>
+        <v>140</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1796,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>325</v>
-      </c>
-      <c r="G34" t="n">
-        <v>68</v>
+        <v>153</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>135</v>
+        <v>1172</v>
       </c>
       <c r="G35" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1878,40 +1880,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>153</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>105</v>
+      </c>
+      <c r="G36" t="n">
+        <v>78</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1156</v>
+        <v>29</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>28</v>
+        <v>933</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2044,38 +2044,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>1159</v>
       </c>
       <c r="G40" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -2085,38 +2085,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>925</v>
+        <v>2063</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -2126,118 +2126,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1143</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>北京·原神only3.0</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>北花园路1号 超级蜂巢</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>2061</v>
-      </c>
-      <c r="G43" t="n">
-        <v>68</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>4</v>
-      </c>
-      <c r="G44" t="n">
-        <v>55</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2409,7 +2327,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2591,7 +2509,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2659,7 +2577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2814,7 +2732,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2937,7 +2855,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3762</v>
+        <v>3768</v>
       </c>
       <c r="G7" t="n">
         <v>85</v>
@@ -2964,33 +2882,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3762</v>
+        <v>298</v>
       </c>
       <c r="G8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,7 +2923,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3019,19 +2937,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>295</v>
+        <v>5315</v>
       </c>
       <c r="G9" t="n">
         <v>80</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -3041,38 +2959,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5301</v>
+        <v>600</v>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -3087,33 +3005,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>590</v>
+        <v>435</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3123,38 +3041,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>426</v>
+        <v>229</v>
       </c>
       <c r="G12" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3169,33 +3087,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>229</v>
+        <v>1069</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3205,38 +3123,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1062</v>
-      </c>
-      <c r="G14" t="n">
-        <v>55</v>
+        <v>290</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3251,35 +3171,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>290</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>146</v>
+      </c>
+      <c r="G15" t="n">
+        <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3294,33 +3212,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3349,19 +3267,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>735</v>
       </c>
       <c r="G17" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3376,33 +3294,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>731</v>
+        <v>370</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3417,33 +3335,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>364</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3371,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G20" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3412,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,33 +3458,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,33 +3499,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>179</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3535,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>372</v>
       </c>
       <c r="G24" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,33 +3581,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>370</v>
+        <v>6094</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>70.2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3622,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3714,23 +3632,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6068</v>
+        <v>48</v>
       </c>
       <c r="G26" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3663,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3762,16 +3680,16 @@
         <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3704,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3796,23 +3714,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3827,12 +3745,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3841,19 +3759,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>7038</v>
       </c>
       <c r="G29" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3781,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6826</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3827,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3926,16 +3844,16 @@
         <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3863,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>3265</v>
       </c>
       <c r="G32" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,12 +3909,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4005,19 +3923,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3260</v>
+        <v>375</v>
       </c>
       <c r="G33" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -4032,33 +3950,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>371</v>
+        <v>757</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -4073,33 +3991,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>752</v>
+        <v>4463</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -4109,38 +4027,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4460</v>
+        <v>325</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4150,38 +4068,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>325</v>
+        <v>31</v>
       </c>
       <c r="G37" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4191,38 +4109,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4232,38 +4150,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>135</v>
-      </c>
-      <c r="G39" t="n">
-        <v>88</v>
+        <v>153</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4278,35 +4198,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>153</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1172</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,38 +4234,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1156</v>
+        <v>105</v>
       </c>
       <c r="G41" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4275,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="G42" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4398,38 +4316,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4439,38 +4357,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>933</v>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4485,33 +4403,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>925</v>
+        <v>1159</v>
       </c>
       <c r="G45" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4521,38 +4439,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1143</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>8.800000000000001</v>
+        <v>380</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4567,33 +4485,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>2063</v>
       </c>
       <c r="G47" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4608,33 +4526,33 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2061</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4644,77 +4562,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="G49" t="n">
-        <v>55</v>
+        <v>680</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>66</v>
-      </c>
-      <c r="G50" t="n">
-        <v>680</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023.12.22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -523,7 +523,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024.01.26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3768</v>
+        <v>300</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>298</v>
+        <v>5336</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5315</v>
+        <v>613</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>600</v>
+        <v>451</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>435</v>
+        <v>239</v>
       </c>
       <c r="G8" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>229</v>
+        <v>1098</v>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1069</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
+        <v>289</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -851,40 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>290</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>155</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,17 +935,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -954,19 +954,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>746</v>
       </c>
       <c r="G13" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>735</v>
+        <v>377</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>370</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>182</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>373</v>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1222,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>372</v>
+        <v>6150</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1278,23 +1278,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6094</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,17 +1386,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1405,19 +1405,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>7101</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7038</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,17 +1468,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1490,16 +1490,16 @@
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>3269</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1569,19 +1569,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3265</v>
+        <v>384</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>375</v>
+        <v>772</v>
       </c>
       <c r="G29" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>757</v>
+        <v>4467</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1673,38 +1673,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4463</v>
+        <v>326</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1714,38 +1714,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>325</v>
+        <v>144</v>
       </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1755,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>140</v>
-      </c>
-      <c r="G33" t="n">
-        <v>88</v>
+        <v>153</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,40 +1798,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>153</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1196</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1172</v>
+        <v>109</v>
       </c>
       <c r="G35" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1880,38 +1880,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>952</v>
       </c>
       <c r="G38" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,38 +2003,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>933</v>
+        <v>1200</v>
       </c>
       <c r="G39" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -2044,38 +2044,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1159</v>
+        <v>2064</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>68</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -2085,77 +2085,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2063</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" t="n">
-        <v>55</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2226,7 +2185,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2267,7 +2226,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2308,7 +2267,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2349,7 +2308,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024.05.25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2449,7 +2408,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023.12.22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2468,7 +2427,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2490,7 +2449,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2023.12.29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2509,7 +2468,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2531,7 +2490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024.01.26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2550,7 +2509,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2577,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2631,7 +2590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023.12.22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2650,7 +2609,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2672,7 +2631,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023.12.22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2691,7 +2650,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2713,7 +2672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2023.12.29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2732,7 +2691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2754,7 +2713,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024.01.26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2773,7 +2732,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2795,7 +2754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024.01.26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2836,38 +2795,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·ICOS SP漫展03</t>
+          <t>北京·Look&amp;thebONE情人节专场</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>太平庄中街西端 北京天通苑黄河京都会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 09:00-02.14 17:00</t>
+          <t>2024.02.13 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3768</v>
+        <v>300</v>
       </c>
       <c r="G7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77992</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/MQV2WfTg1707199914411.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2836,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·thebONE游戏动漫节</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2896,19 +2855,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>298</v>
+        <v>5336</v>
       </c>
       <c r="G8" t="n">
         <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
         </is>
       </c>
     </row>
@@ -2918,38 +2877,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-13</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5315</v>
+        <v>613</v>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -2959,38 +2918,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>600</v>
+        <v>451</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>21.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -3000,38 +2959,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>435</v>
+        <v>239</v>
       </c>
       <c r="G11" t="n">
-        <v>21.9</v>
+        <v>48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3041,38 +3000,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>229</v>
+        <v>1098</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -3082,38 +3041,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1069</v>
-      </c>
-      <c r="G13" t="n">
-        <v>55</v>
+        <v>289</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3123,40 +3084,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>290</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>155</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3125,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -3207,17 +3166,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3226,19 +3185,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>746</v>
       </c>
       <c r="G16" t="n">
-        <v>9.9</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3248,38 +3207,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>735</v>
+        <v>377</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3289,38 +3248,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>370</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3330,38 +3289,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3330,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G20" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3371,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3412,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>182</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3453,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>373</v>
       </c>
       <c r="G23" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3494,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>372</v>
+        <v>6150</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3535,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3591,23 +3550,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6094</v>
+        <v>49</v>
       </c>
       <c r="G25" t="n">
-        <v>70.2</v>
+        <v>238</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3576,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3636,19 +3595,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3617,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3673,23 +3632,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,17 +3658,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3718,19 +3677,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>7101</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3699,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7038</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,17 +3740,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3803,16 +3762,16 @@
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3781,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>3269</v>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3822,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3882,19 +3841,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3265</v>
+        <v>384</v>
       </c>
       <c r="G32" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3863,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>375</v>
+        <v>772</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3904,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>757</v>
+        <v>4467</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3945,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4463</v>
+        <v>326</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4027,38 +3986,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>325</v>
+        <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,38 +4027,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4109,38 +4068,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>140</v>
-      </c>
-      <c r="G38" t="n">
-        <v>88</v>
+        <v>153</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4150,40 +4111,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>153</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1196</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4152,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1172</v>
+        <v>109</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4193,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4234,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,38 +4275,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>952</v>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4316,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>933</v>
+        <v>1200</v>
       </c>
       <c r="G44" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4398,38 +4357,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1159</v>
+        <v>15</v>
       </c>
       <c r="G45" t="n">
-        <v>8.800000000000001</v>
+        <v>380</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4439,38 +4398,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>2064</v>
       </c>
       <c r="G46" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4480,38 +4439,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2063</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4521,77 +4480,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024.05.25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="G48" t="n">
-        <v>55</v>
+        <v>680</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024-05-25</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>66</v>
-      </c>
-      <c r="G49" t="n">
-        <v>680</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G4" t="n">
         <v>80</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5336</v>
+        <v>5338</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="G7" t="n">
         <v>21.9</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G8" t="n">
         <v>48</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1098</v>
+        <v>1115</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G12" t="n">
         <v>9.9</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="G14" t="n">
         <v>85</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
         <v>66</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G17" t="n">
         <v>93</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6150</v>
+        <v>6175</v>
       </c>
       <c r="G20" t="n">
         <v>78</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
         <v>128</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7101</v>
+        <v>7151</v>
       </c>
       <c r="G24" t="n">
         <v>63</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3269</v>
+        <v>3276</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4467</v>
+        <v>4469</v>
       </c>
       <c r="G30" t="n">
         <v>75</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G31" t="n">
         <v>68</v>
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G32" t="n">
         <v>88</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1196</v>
+        <v>1218</v>
       </c>
       <c r="G34" t="n">
         <v>8.800000000000001</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G35" t="n">
         <v>78</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
         <v>55</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>952</v>
+        <v>965</v>
       </c>
       <c r="G38" t="n">
         <v>75</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1200</v>
+        <v>1231</v>
       </c>
       <c r="G39" t="n">
         <v>8.800000000000001</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="G40" t="n">
         <v>68</v>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>55</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2536,7 +2536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G7" t="n">
         <v>80</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5336</v>
+        <v>5338</v>
       </c>
       <c r="G8" t="n">
         <v>80</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="G10" t="n">
         <v>21.9</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G11" t="n">
         <v>48</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1098</v>
+        <v>1115</v>
       </c>
       <c r="G12" t="n">
         <v>55</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
         <v>9.9</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="G17" t="n">
         <v>85</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
         <v>66</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G19" t="n">
         <v>88</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G21" t="n">
         <v>93</v>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6150</v>
+        <v>6175</v>
       </c>
       <c r="G24" t="n">
         <v>78</v>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3550,23 +3550,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>49</v>
+        <v>6175</v>
       </c>
       <c r="G25" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3595,19 +3595,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3632,23 +3632,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3677,19 +3677,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7101</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3699,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>7151</v>
       </c>
       <c r="G29" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,12 +3745,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3762,16 +3762,16 @@
         <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>128</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3781,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3269</v>
+        <v>25</v>
       </c>
       <c r="G31" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3827,12 +3827,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3841,19 +3841,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>384</v>
+        <v>3276</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3868,33 +3868,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>772</v>
+        <v>395</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3909,33 +3909,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4467</v>
+        <v>781</v>
       </c>
       <c r="G34" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3945,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>326</v>
+        <v>4469</v>
       </c>
       <c r="G35" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3986,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.27</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>31</v>
+        <v>329</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -4027,38 +4027,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,40 +4068,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>153</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>149</v>
+      </c>
+      <c r="G38" t="n">
+        <v>88</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4116,33 +4114,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1196</v>
-      </c>
-      <c r="G39" t="n">
-        <v>8.800000000000001</v>
+        <v>154</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4152,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>109</v>
+        <v>1218</v>
       </c>
       <c r="G40" t="n">
-        <v>78</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4193,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4234,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G42" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4275,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>952</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4321,33 +4321,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1200</v>
+        <v>965</v>
       </c>
       <c r="G44" t="n">
-        <v>8.800000000000001</v>
+        <v>75</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4357,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>1231</v>
       </c>
       <c r="G45" t="n">
-        <v>380</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4403,33 +4403,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2064</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4444,33 +4444,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>2066</v>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4480,36 +4480,77 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2024.05.18</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>北京·次元风暴游园会2.0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2024.05.18 09:00-05.19 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>5</v>
+      </c>
+      <c r="G48" t="n">
+        <v>55</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>2024.05.25</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>66</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="F49" t="n">
+        <v>68</v>
+      </c>
+      <c r="G49" t="n">
         <v>680</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.13</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>301</v>
+        <v>635</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.13</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5338</v>
+        <v>473</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>21.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>620</v>
+        <v>260</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>462</v>
+        <v>1144</v>
       </c>
       <c r="G7" t="n">
-        <v>21.9</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>245</v>
-      </c>
-      <c r="G8" t="n">
-        <v>48</v>
+        <v>289</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -769,38 +771,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1115</v>
+        <v>175</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,35 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>289</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -858,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>164</v>
+        <v>763</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -899,33 +899,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>58</v>
+        <v>407</v>
       </c>
       <c r="G12" t="n">
-        <v>9.9</v>
+        <v>85</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>749</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>388</v>
+        <v>98</v>
       </c>
       <c r="G14" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>199</v>
       </c>
       <c r="G15" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>193</v>
+        <v>383</v>
       </c>
       <c r="G17" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>6230</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>378</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1237,23 +1237,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6175</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1278,23 +1278,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1309,33 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>7202</v>
       </c>
       <c r="G22" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>7151</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1427,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>3291</v>
       </c>
       <c r="G25" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>415</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1514,33 +1514,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3276</v>
+        <v>791</v>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1555,33 +1555,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>395</v>
+        <v>4475</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>781</v>
+        <v>331</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4469</v>
+        <v>155</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1673,38 +1673,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>329</v>
-      </c>
-      <c r="G31" t="n">
-        <v>68</v>
+        <v>156</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>149</v>
+        <v>1267</v>
       </c>
       <c r="G32" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,40 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>154</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>116</v>
+      </c>
+      <c r="G33" t="n">
+        <v>78</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1798,38 +1798,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1218</v>
+        <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -1880,38 +1880,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>33</v>
+        <v>990</v>
       </c>
       <c r="G36" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>1287</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -1962,38 +1962,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>965</v>
+        <v>2073</v>
       </c>
       <c r="G38" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -2003,118 +2003,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1231</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>北京·原神only3.0</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>北花园路1号 超级蜂巢</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>2066</v>
-      </c>
-      <c r="G40" t="n">
-        <v>68</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" t="n">
-        <v>55</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2245,7 +2163,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2327,7 +2245,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2427,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2468,7 +2386,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2509,7 +2427,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2536,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2609,7 +2527,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2691,7 +2609,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2732,7 +2650,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2795,38 +2713,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.13</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·Look&amp;thebONE情人节专场</t>
+          <t>北京·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 10:00-02.16 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>301</v>
+        <v>635</v>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79089</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/pTqByZ2i1703668576004.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
         </is>
       </c>
     </row>
@@ -2836,38 +2754,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.13</t>
+          <t>2024.02.16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·thebONE游戏动漫节</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.13 10:00-02.15 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5338</v>
+        <v>473</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>21.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79611</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/5br38n1G1703644868437.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -2877,38 +2795,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.17 13:00-02.18 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>620</v>
+        <v>260</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -2918,38 +2836,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>462</v>
+        <v>1144</v>
       </c>
       <c r="G10" t="n">
-        <v>21.9</v>
+        <v>55</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -2959,38 +2877,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>245</v>
-      </c>
-      <c r="G11" t="n">
-        <v>48</v>
+        <v>289</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -3000,38 +2920,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1115</v>
+        <v>175</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,35 +2966,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>289</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -3089,33 +3007,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>164</v>
+        <v>763</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -3130,33 +3048,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>407</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>85</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3171,33 +3089,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>749</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3207,38 +3125,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>388</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3248,38 +3166,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="G18" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3289,38 +3207,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="G19" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3253,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3349,19 +3267,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,38 +3289,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>193</v>
+        <v>383</v>
       </c>
       <c r="G21" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3330,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>6230</v>
       </c>
       <c r="G22" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3458,33 +3376,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>378</v>
+        <v>6230</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3417,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3509,23 +3427,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6175</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3458,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3550,23 +3468,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6175</v>
+        <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3591,23 +3509,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3622,33 +3540,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>52</v>
+        <v>7202</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3658,12 +3576,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3673,23 +3591,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3617,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7151</v>
+        <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3658,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>25</v>
+        <v>3291</v>
       </c>
       <c r="G30" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3699,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>415</v>
       </c>
       <c r="G31" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3827,33 +3745,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3276</v>
+        <v>791</v>
       </c>
       <c r="G32" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3868,33 +3786,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>395</v>
+        <v>4475</v>
       </c>
       <c r="G33" t="n">
         <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3822,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>781</v>
+        <v>331</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -3945,38 +3863,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4469</v>
+        <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -3986,38 +3904,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>329</v>
+        <v>155</v>
       </c>
       <c r="G36" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +3945,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.03.27</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
-      </c>
-      <c r="G37" t="n">
-        <v>60</v>
+        <v>156</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,38 +3988,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>149</v>
+        <v>1267</v>
       </c>
       <c r="G38" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -4109,40 +4029,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>154</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>116</v>
+      </c>
+      <c r="G39" t="n">
+        <v>78</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4070,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1218</v>
+        <v>37</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4111,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4152,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>33</v>
+        <v>990</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4193,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>1287</v>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,38 +4234,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>965</v>
+        <v>15</v>
       </c>
       <c r="G44" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4357,38 +4275,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1231</v>
+        <v>2073</v>
       </c>
       <c r="G45" t="n">
-        <v>8.800000000000001</v>
+        <v>68</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4403,33 +4321,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4439,118 +4357,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024.05.25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2066</v>
+        <v>70</v>
       </c>
       <c r="G47" t="n">
-        <v>68</v>
+        <v>680</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>5</v>
-      </c>
-      <c r="G48" t="n">
-        <v>55</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2024.05.25</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>68</v>
-      </c>
-      <c r="G49" t="n">
-        <v>680</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
         <v>68</v>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="G5" t="n">
         <v>21.9</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G6" t="n">
         <v>48</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
         <v>9.9</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="G12" t="n">
         <v>85</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
         <v>66</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G15" t="n">
         <v>93</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6230</v>
+        <v>6254</v>
       </c>
       <c r="G18" t="n">
         <v>78</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G19" t="n">
         <v>238</v>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7202</v>
+        <v>7223</v>
       </c>
       <c r="G22" t="n">
         <v>63</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3291</v>
+        <v>3294</v>
       </c>
       <c r="G25" t="n">
         <v>58</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G26" t="n">
         <v>75</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4475</v>
+        <v>4477</v>
       </c>
       <c r="G28" t="n">
         <v>75</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G29" t="n">
         <v>68</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G30" t="n">
         <v>88</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1267</v>
+        <v>1293</v>
       </c>
       <c r="G32" t="n">
         <v>8.800000000000001</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G33" t="n">
         <v>78</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>990</v>
+        <v>1009</v>
       </c>
       <c r="G36" t="n">
         <v>75</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1287</v>
+        <v>1319</v>
       </c>
       <c r="G37" t="n">
         <v>8.800000000000001</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="G38" t="n">
         <v>68</v>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2454,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>68</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="G8" t="n">
         <v>21.9</v>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G9" t="n">
         <v>48</v>
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="G10" t="n">
         <v>55</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
         <v>9.9</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="G15" t="n">
         <v>85</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
         <v>66</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
         <v>88</v>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G19" t="n">
         <v>93</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6230</v>
+        <v>6254</v>
       </c>
       <c r="G22" t="n">
         <v>78</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3386,23 +3386,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6230</v>
+        <v>51</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3431,19 +3431,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G24" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3468,23 +3468,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3513,19 +3513,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>7223</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3535,38 +3535,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7202</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3595,19 +3595,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3617,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>27</v>
+        <v>3294</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3677,19 +3677,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3291</v>
+        <v>420</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3704,33 +3704,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>415</v>
+        <v>798</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3745,33 +3745,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>791</v>
+        <v>4477</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3781,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4475</v>
+        <v>332</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3822,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c r="G34" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3863,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.03.27</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -3904,38 +3904,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>155</v>
-      </c>
-      <c r="G36" t="n">
-        <v>88</v>
+        <v>158</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3950,35 +3952,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>156</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1293</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +3988,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1267</v>
+        <v>122</v>
       </c>
       <c r="G38" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +4029,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="G39" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,38 +4070,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4111,38 +4111,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>1009</v>
       </c>
       <c r="G41" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4157,33 +4157,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>990</v>
+        <v>1319</v>
       </c>
       <c r="G42" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4193,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1287</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
-        <v>8.800000000000001</v>
+        <v>380</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>2079</v>
       </c>
       <c r="G44" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4280,33 +4280,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2073</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,77 +4316,36 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024.05.25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="G46" t="n">
-        <v>55</v>
+        <v>680</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2024.05.25</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>70</v>
-      </c>
-      <c r="G47" t="n">
-        <v>680</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -569,33 +569,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>642</v>
+        <v>498</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>21.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>484</v>
+        <v>1183</v>
       </c>
       <c r="G5" t="n">
-        <v>21.9</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>263</v>
-      </c>
-      <c r="G6" t="n">
-        <v>48</v>
+        <v>289</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -687,38 +689,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1153</v>
+        <v>198</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,35 +735,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>289</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>178</v>
+        <v>779</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -817,33 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>427</v>
       </c>
       <c r="G10" t="n">
-        <v>9.9</v>
+        <v>85</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -858,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>767</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.02 13:00-03.03 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>415</v>
+        <v>267</v>
       </c>
       <c r="G12" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="G13" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,33 +981,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>203</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>389</v>
       </c>
       <c r="G16" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>383</v>
+        <v>6308</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6254</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1200,19 +1200,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G19" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1237,23 +1237,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1282,19 +1282,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>7270</v>
       </c>
       <c r="G21" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7223</v>
+        <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1364,19 +1364,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>3307</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1446,19 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3294</v>
+        <v>435</v>
       </c>
       <c r="G25" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1473,33 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>420</v>
+        <v>813</v>
       </c>
       <c r="G26" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1514,33 +1514,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>798</v>
+        <v>4481</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4477</v>
+        <v>336</v>
       </c>
       <c r="G28" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>332</v>
+        <v>166</v>
       </c>
       <c r="G29" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1632,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>158</v>
-      </c>
-      <c r="G30" t="n">
-        <v>88</v>
+        <v>165</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1678,35 +1680,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>158</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1320</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1293</v>
+        <v>126</v>
       </c>
       <c r="G32" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1757,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="G33" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1798,38 +1798,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>1033</v>
       </c>
       <c r="G35" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -1885,33 +1885,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1009</v>
+        <v>1372</v>
       </c>
       <c r="G36" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1319</v>
+        <v>2091</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>68</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,31 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2079</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>6</v>
-      </c>
-      <c r="G39" t="n">
-        <v>55</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2163,7 +2122,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2386,7 +2345,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2427,7 +2386,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2454,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,7 +2527,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G3" t="n">
         <v>88</v>
@@ -2609,7 +2568,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2650,7 +2609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2718,33 +2677,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·原神X星穹铁道ONLY</t>
+          <t>北京·古谷PLAZA(谷子市集)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.16 17:00</t>
+          <t>2024.02.16 13:00-02.17 17:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>642</v>
+        <v>498</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>21.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79517</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/80rheYUy1702003360938.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
         </is>
       </c>
     </row>
@@ -2754,38 +2713,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t>北京·第五届璃樱动漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>484</v>
+        <v>1183</v>
       </c>
       <c r="G8" t="n">
-        <v>21.9</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
         </is>
       </c>
     </row>
@@ -2795,38 +2754,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.17 13:00-02.18 19:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>263</v>
-      </c>
-      <c r="G9" t="n">
-        <v>48</v>
+        <v>289</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -2836,38 +2797,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1153</v>
+        <v>198</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2882,35 +2843,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>289</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -2925,33 +2884,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>178</v>
+        <v>779</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -2966,33 +2925,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>427</v>
       </c>
       <c r="G13" t="n">
-        <v>9.9</v>
+        <v>85</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -3007,33 +2966,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>767</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -3043,38 +3002,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.02 13:00-03.03 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>415</v>
+        <v>267</v>
       </c>
       <c r="G15" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -3084,38 +3043,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3084,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3171,33 +3130,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>98</v>
+        <v>206</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3212,33 +3171,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>203</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3248,38 +3207,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>389</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3294,33 +3253,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>383</v>
+        <v>6308</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3294,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3345,23 +3304,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6254</v>
+        <v>51</v>
       </c>
       <c r="G22" t="n">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3335,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3390,19 +3349,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3376,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3427,23 +3386,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3417,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3472,19 +3431,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>7270</v>
       </c>
       <c r="G25" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3453,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7223</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3499,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3554,19 +3513,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G27" t="n">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3576,38 +3535,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>27</v>
+        <v>3307</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3581,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3636,19 +3595,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3294</v>
+        <v>435</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3663,33 +3622,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>420</v>
+        <v>813</v>
       </c>
       <c r="G30" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3704,33 +3663,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>798</v>
+        <v>4481</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3699,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4477</v>
+        <v>336</v>
       </c>
       <c r="G32" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3740,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>332</v>
+        <v>37</v>
       </c>
       <c r="G33" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,38 +3781,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.27</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -3863,38 +3822,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>158</v>
-      </c>
-      <c r="G35" t="n">
-        <v>88</v>
+        <v>165</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3909,35 +3870,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>158</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1320</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -3947,38 +3906,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1293</v>
+        <v>126</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>78</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +3947,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="G38" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +3988,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,38 +4029,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>1033</v>
       </c>
       <c r="G40" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -4116,33 +4075,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1009</v>
+        <v>1372</v>
       </c>
       <c r="G41" t="n">
-        <v>75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4111,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1319</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>8.800000000000001</v>
+        <v>380</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4198,33 +4157,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>2091</v>
       </c>
       <c r="G43" t="n">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4239,33 +4198,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2079</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,77 +4234,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024.05.25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会2.0</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="G45" t="n">
-        <v>55</v>
+        <v>680</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2024.05.25</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>70</v>
-      </c>
-      <c r="G46" t="n">
-        <v>680</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G4" t="n">
         <v>21.9</v>
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G8" t="n">
         <v>9.9</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="G10" t="n">
         <v>85</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
         <v>66</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G12" t="n">
         <v>48</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G14" t="n">
         <v>93</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6308</v>
+        <v>6337</v>
       </c>
       <c r="G17" t="n">
         <v>78</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
         <v>238</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G19" t="n">
         <v>128</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7270</v>
+        <v>7307</v>
       </c>
       <c r="G21" t="n">
         <v>63</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3307</v>
+        <v>3319</v>
       </c>
       <c r="G24" t="n">
         <v>58</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G25" t="n">
         <v>75</v>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4481</v>
+        <v>4485</v>
       </c>
       <c r="G27" t="n">
         <v>75</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G28" t="n">
         <v>68</v>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G29" t="n">
         <v>88</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1320</v>
+        <v>1342</v>
       </c>
       <c r="G31" t="n">
         <v>8.800000000000001</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G32" t="n">
         <v>78</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="G35" t="n">
         <v>75</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1372</v>
+        <v>1420</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="G37" t="n">
         <v>68</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G7" t="n">
         <v>21.9</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
         <v>9.9</v>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="G13" t="n">
         <v>85</v>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
         <v>66</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
         <v>88</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G18" t="n">
         <v>93</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6308</v>
+        <v>6337</v>
       </c>
       <c r="G21" t="n">
         <v>78</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
         <v>238</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G23" t="n">
         <v>128</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7270</v>
+        <v>7307</v>
       </c>
       <c r="G25" t="n">
         <v>63</v>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3307</v>
+        <v>3319</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>813</v>
+        <v>823</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4481</v>
+        <v>4485</v>
       </c>
       <c r="G31" t="n">
         <v>75</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G32" t="n">
         <v>68</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G34" t="n">
         <v>88</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1320</v>
+        <v>1342</v>
       </c>
       <c r="G36" t="n">
         <v>8.800000000000001</v>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G37" t="n">
         <v>78</v>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1033</v>
+        <v>1052</v>
       </c>
       <c r="G40" t="n">
         <v>75</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1372</v>
+        <v>1420</v>
       </c>
       <c r="G41" t="n">
         <v>8.800000000000001</v>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="G43" t="n">
         <v>68</v>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,38 +564,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>504</v>
-      </c>
-      <c r="G4" t="n">
-        <v>21.9</v>
+        <v>290</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -605,38 +607,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1188</v>
+        <v>224</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,35 +653,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>289</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -694,33 +694,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>205</v>
+        <v>794</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -735,33 +735,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>73</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>9.9</v>
+        <v>85</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -776,33 +776,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>782</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +812,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.02 13:00-03.03 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>433</v>
+        <v>277</v>
       </c>
       <c r="G10" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +853,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.03 19:00</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="G12" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -954,19 +954,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>208</v>
+        <v>395</v>
       </c>
       <c r="G14" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>6393</v>
       </c>
       <c r="G15" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>389</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1114,23 +1114,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6337</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -1186,33 +1186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>7354</v>
       </c>
       <c r="G19" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1237,23 +1237,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7307</v>
+        <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1304,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>3330</v>
       </c>
       <c r="G22" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>762</v>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -1391,33 +1391,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3319</v>
+        <v>843</v>
       </c>
       <c r="G24" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -1432,33 +1432,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>442</v>
+        <v>4492</v>
       </c>
       <c r="G25" t="n">
         <v>75</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1468,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>823</v>
+        <v>338</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1509,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4485</v>
+        <v>175</v>
       </c>
       <c r="G27" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>338</v>
-      </c>
-      <c r="G28" t="n">
-        <v>68</v>
+        <v>169</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1593,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>168</v>
+        <v>1387</v>
       </c>
       <c r="G29" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,40 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>165</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>133</v>
+      </c>
+      <c r="G30" t="n">
+        <v>78</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1342</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -1757,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>39</v>
+        <v>1079</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -1798,38 +1798,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>1494</v>
       </c>
       <c r="G34" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1052</v>
+        <v>2105</v>
       </c>
       <c r="G35" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -1880,118 +1880,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1420</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>北京·原神only3.0</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>北花园路1号 超级蜂巢</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>2093</v>
-      </c>
-      <c r="G37" t="n">
-        <v>68</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>6</v>
-      </c>
-      <c r="G38" t="n">
-        <v>55</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
@@ -2081,7 +1999,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>88</v>
@@ -2122,7 +2040,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
@@ -2163,7 +2081,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2204,7 +2122,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
         <v>680</v>
@@ -2304,7 +2222,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2345,7 +2263,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1181</v>
+        <v>1191</v>
       </c>
       <c r="G3" t="n">
         <v>20</v>
@@ -2386,7 +2304,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2413,7 +2331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2486,7 +2404,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G2" t="n">
         <v>30</v>
@@ -2568,7 +2486,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1181</v>
+        <v>1191</v>
       </c>
       <c r="G4" t="n">
         <v>20</v>
@@ -2609,7 +2527,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -2672,38 +2590,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024.02.16</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>北京·古谷PLAZA(谷子市集)</t>
+          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>东打磨厂街7号宝鼎中心A座 新活馆</t>
+          <t>荣华中路国融国际 大兴云果国潮</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.16 13:00-02.17 17:30</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>504</v>
-      </c>
-      <c r="G7" t="n">
-        <v>21.9</v>
+        <v>290</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80648</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Uap4GSw41704789232576.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
         </is>
       </c>
     </row>
@@ -2713,38 +2633,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024.02.17</t>
+          <t>2024.02.24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>北京·第五届璃樱动漫嘉年华</t>
+          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 14:00-02.25 20:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1188</v>
+        <v>224</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/BPibBCHv1702005490875.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,35 +2679,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 北京·2024年新春次元嘉年华（取消）</t>
+          <t>北京·ILOVE谷玩市场</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>荣华中路国融国际 大兴云果国潮</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>289</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77369</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/BXg0AxJD1706166580169.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
         </is>
       </c>
     </row>
@@ -2802,33 +2720,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>北京·A+国潮动漫嘉年华（免费展会）</t>
+          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>东坝中路38号 北京金隅嘉品Mall中庭</t>
+          <t>望京西路41号 望京信万广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.24 14:00-02.25 20:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>205</v>
+        <v>794</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81655</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/YJ5b9tOr1706843979777.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
         </is>
       </c>
     </row>
@@ -2843,33 +2761,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>北京·ILOVE谷玩市场</t>
+          <t>北京·回声动漫轰趴节</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 13:00-02.25 02:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>453</v>
       </c>
       <c r="G11" t="n">
-        <v>9.9</v>
+        <v>85</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81594</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/je6hgR261707286957960.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
         </is>
       </c>
     </row>
@@ -2884,33 +2802,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京·LY动漫游戏嘉年华-闹元宵</t>
+          <t>北京·陵云之境代号鸢only</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>望京西路41号 望京信万广场</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.24 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>782</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81504</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/OGr3XdLb1706523654421.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
         </is>
       </c>
     </row>
@@ -2920,38 +2838,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京·回声动漫轰趴节</t>
+          <t>北京·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>广渠东路一号创1958园区3-11号 echoo回声空间</t>
+          <t>东坝中路38号 金隅嘉品MALL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 02:00</t>
+          <t>2024.03.02 13:00-03.03 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>433</v>
+        <v>277</v>
       </c>
       <c r="G13" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81219</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/fud8fFxQ1705908806310.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
         </is>
       </c>
     </row>
@@ -2961,38 +2879,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024.02.24</t>
+          <t>2024.03.03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京·陵云之境代号鸢only</t>
+          <t>北京·次元音浪——少女派对</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.24 17:00</t>
+          <t>2024.03.03 13:00-03.03 16:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81625</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/1MTnYyt81706774517447.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
         </is>
       </c>
     </row>
@@ -3002,38 +2920,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024.03.02</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京·SISP动漫游戏嘉年华</t>
+          <t>北京·ACG GO·岁末游园会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>东坝中路38号 金隅嘉品MALL</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.03 19:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80337</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/WWzwlVj21703832184459.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3043,38 +2961,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024.03.03</t>
+          <t>2024.03.09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>北京·次元音浪——少女派对</t>
+          <t>北京·VOCALOID ONLY同人展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>日坛北路17号日坛公园北门对面 METAL BOX</t>
+          <t>永外高庄138号 大红门国际会展中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.03 13:00-03.03 16:30</t>
+          <t>2024.03.09 12:00-03.09 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="G16" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80650</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/n6NziI6Q1706524633903.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
         </is>
       </c>
     </row>
@@ -3089,12 +3007,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>北京·ACG GO·岁末游园会</t>
+          <t>北京·第三届次元潮流动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3103,19 +3021,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80347</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/EgfGaYzy1704349024872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
         </is>
       </c>
     </row>
@@ -3125,38 +3043,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>北京·VOCALOID ONLY同人展</t>
+          <t>北京· YiYou 运动番only 2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>永外高庄138号 大红门国际会展中心</t>
+          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 12:00-03.09 19:00</t>
+          <t>2024.03.16 09:30-03.17 18:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>208</v>
+        <v>395</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81043</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/CiMBnoFr1705567758852.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
         </is>
       </c>
     </row>
@@ -3166,38 +3084,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024.03.09</t>
+          <t>2024.03.16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>北京·第三届次元潮流动漫嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>方庄芳古园一区18号楼 北京NTP新城广场</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>6393</v>
       </c>
       <c r="G19" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/ZmPl8yMs1707201201332.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
         </is>
       </c>
     </row>
@@ -3212,33 +3130,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京· YiYou 运动番only 2.0</t>
+          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>京开高速入口与京开高速交叉口西180米 北京双马文体创业园</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.16 09:30-03.17 18:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>389</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78902</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/GKhgeikt1700729687027.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3171,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th- 来自异世界的召唤</t>
+          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3263,23 +3181,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6337</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/O9Uv3FBk1705486323502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3212,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th凌飞专场见面会</t>
+          <t>北京·TCS卡牌嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3304,23 +3222,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81605</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/btRWOE8s1706769469249.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
         </is>
       </c>
     </row>
@@ -3335,33 +3253,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th钱琛专场见面会</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>62</v>
+        <v>7354</v>
       </c>
       <c r="G23" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81603</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ceaoj1d31706768982944.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3289,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京·TCS卡牌嘉年华</t>
+          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3386,23 +3304,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81443</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/080XUrv51706238170152.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
         </is>
       </c>
     </row>
@@ -3412,38 +3330,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024.03.16</t>
+          <t>2024.03.17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华02</t>
+          <t>北京·THP 03 白兔茶话会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 17:00</t>
+          <t>2024.03.17 10:00-03.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7307</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78896</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/U4lCMJJL1706088767412.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
         </is>
       </c>
     </row>
@@ -3453,38 +3371,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京·Aw动漫游戏嘉年华7th紫枫儿专场见面会</t>
+          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>26</v>
+        <v>3330</v>
       </c>
       <c r="G26" t="n">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/Zx0J7Vz21706769083195.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
         </is>
       </c>
     </row>
@@ -3494,38 +3412,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024.03.17</t>
+          <t>2024.03.23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京·THP 03 白兔茶话会</t>
+          <t>北京·万游引力国潮动漫嘉年华s6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>三间房乡建国路16号院星空文娱C区2层东A201室 梦与宝藏（珠江绿洲家园店）</t>
+          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.17 10:00-03.17 17:00</t>
+          <t>2024.03.23 10:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>762</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81775</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/hNH1GPLb1707186397835.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
         </is>
       </c>
     </row>
@@ -3540,33 +3458,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京·thebONE×Ilike动漫游戏嘉年华S4</t>
+          <t>北京·排球少年ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>永外高庄138号  大红门会展中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 10:00-03.23 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3319</v>
+        <v>843</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79601</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/pSrsMI9z1705646196593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
         </is>
       </c>
     </row>
@@ -3581,33 +3499,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京·万游引力国潮动漫嘉年华s6</t>
+          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>半截塔路53号首创郎园station 郎园station中央车站文化中心</t>
+          <t>石景山路68号 北京首钢会展中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.24 17:00</t>
+          <t>2024.03.23 09:00-03.24 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>442</v>
+        <v>4492</v>
       </c>
       <c r="G29" t="n">
         <v>75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79322</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/pKxWxe3i1707205136326.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
         </is>
       </c>
     </row>
@@ -3617,38 +3535,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京·排球少年ONLY</t>
+          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>永外高庄138号  大红门会展中心</t>
+          <t>学清路38号 金码大厦</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.23 10:00-03.23 17:00</t>
+          <t>2024.03.24 10:30-03.24 18:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>823</v>
+        <v>338</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80510</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/wNTz3awE1704441972575.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
         </is>
       </c>
     </row>
@@ -3658,38 +3576,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024.03.23</t>
+          <t>2024.03.27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京·西山动漫游戏嘉年华·次元漫境冬日派对</t>
+          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>石景山路68号 北京首钢会展中心</t>
+          <t>东三环北路36号 朝阳剧场</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.23 09:00-03.24 17:00</t>
+          <t>2024.03.27 19:30-03.27 21:10</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4485</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76891</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/VFTEz3C11701046733452.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
         </is>
       </c>
     </row>
@@ -3699,38 +3617,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024.03.24</t>
+          <t>2024.03.30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京· 次元音浪Million Mix——音乐番ONLY</t>
+          <t>北京·梦游园3.0代号鸢周年庆Only</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>学清路38号 金码大厦</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.24 10:30-03.24 18:00</t>
+          <t>2024.03.30 10:00-03.30 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>338</v>
+        <v>175</v>
       </c>
       <c r="G32" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81640</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/YhILflVA1706779569395.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
         </is>
       </c>
     </row>
@@ -3740,38 +3658,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024.03.27</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京·跨越二次元ACG神级动漫世界巡回演唱会</t>
+          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>东三环北路36号 朝阳剧场</t>
+          <t>北京展览馆 北京展览馆</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.27 19:30-03.27 21:10</t>
+          <t>2024.04.04 09:30-04.05 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>37</v>
-      </c>
-      <c r="G33" t="n">
-        <v>60</v>
+        <v>169</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81614</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/rAr8lSIU1706772309212.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
         </is>
       </c>
     </row>
@@ -3781,38 +3701,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024.03.30</t>
+          <t>2024.04.04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京·梦游园3.0代号鸢周年庆Only</t>
+          <t>北京·第15届IJOY漫展xCGF游戏节</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.30 17:00</t>
+          <t>2024.04.04 09:00-04.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>168</v>
+        <v>1387</v>
       </c>
       <c r="G34" t="n">
-        <v>88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81584</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/ASPwEB9W1706844758149.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
         </is>
       </c>
     </row>
@@ -3822,40 +3742,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京·IDOx梦次元动漫游戏嘉年华3rd</t>
+          <t>北京·Yok运动番Only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>北京展览馆 北京展览馆</t>
+          <t>宏福路53号 昆仑决世界搏击中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.04 09:30-04.05 17:00</t>
+          <t>2024.04.06 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>165</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>133</v>
+      </c>
+      <c r="G35" t="n">
+        <v>78</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80825</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/NTLMJXBP1705298780296.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
         </is>
       </c>
     </row>
@@ -3865,38 +3783,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024.04.04</t>
+          <t>2024.04.13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京·第15届IJOY漫展xCGF游戏节</t>
+          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>小关路39号 北投购物公园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.04.04 09:00-04.05 17:00</t>
+          <t>2024.04.13 10:00-04.14 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1342</v>
+        <v>44</v>
       </c>
       <c r="G36" t="n">
-        <v>8.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81174</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/EJejgoZa1705892035599.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
         </is>
       </c>
     </row>
@@ -3906,38 +3824,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024.04.06</t>
+          <t>2024.04.20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京·Yok运动番Only</t>
+          <t>北京·次元风暴游园会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宏福路53号 昆仑决世界搏击中心</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.06 10:00-04.06 17:00</t>
+          <t>2024.04.20 09:00-04.21 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81595</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/4lovHrUf1706759539872.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
         </is>
       </c>
     </row>
@@ -3947,38 +3865,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024.04.13</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京·thebONE✖️GOJO超次元嘉年华12nd</t>
+          <t>北京·IDO动漫游戏嘉年华45th</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>小关路39号 北投购物公园</t>
+          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.13 10:00-04.14 17:00</t>
+          <t>2024.05.01 09:30-05.03 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>39</v>
+        <v>1079</v>
       </c>
       <c r="G38" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81708</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/SnU9Txwp1707019834882.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +3906,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024.04.20</t>
+          <t>2024.05.01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京·次元风暴游园会</t>
+          <t>北京·第16届IJOY漫展XCGF游戏节</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
+          <t>北京国家会议中心 北京国家会议中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.04.20 09:00-04.21 17:00</t>
+          <t>2024.05.01 09:00-05.04 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>1494</v>
       </c>
       <c r="G39" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81781</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/QsBPojEU1707191707677.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +3947,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京·IDO动漫游戏嘉年华45th</t>
+          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>亦庄荣昌东街6号 北京亦创国际会展中心</t>
+          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 09:30-05.03 17:00</t>
+          <t>2024.05.18 20:00-05.18 22:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1052</v>
+        <v>17</v>
       </c>
       <c r="G40" t="n">
-        <v>75</v>
+        <v>380</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80645</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/rrPkZdF81704786315359.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,38 +3988,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024.05.01</t>
+          <t>2024.05.18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京·第16届IJOY漫展XCGF游戏节</t>
+          <t>北京·原神only3.0</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>北京国家会议中心 北京国家会议中心</t>
+          <t>北花园路1号 超级蜂巢</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.05.01 09:00-05.04 17:00</t>
+          <t>2024.05.18 10:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1420</v>
+        <v>2105</v>
       </c>
       <c r="G41" t="n">
-        <v>8.800000000000001</v>
+        <v>68</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81183</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/H86O2Jvv1707017473134.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
         </is>
       </c>
     </row>
@@ -4116,33 +4034,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京·Rie fu日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>北京·次元风暴游园会2.0</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>奥园西路1号院4-5号楼 福浪LiveHouse</t>
+          <t>安翔路1号院 老故事503文化创意产业园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.05.18 20:00-05.18 22:00</t>
+          <t>2024.05.18 09:00-05.19 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>380</v>
+        <v>55</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81445</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/6e9JD6401706239890264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
         </is>
       </c>
     </row>
@@ -4152,118 +4070,36 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024.05.18</t>
+          <t>2024.05.25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京·原神only3.0</t>
+          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>北花园路1号 超级蜂巢</t>
+          <t>东直门南大街14号 北京保利剧院</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.05.18 10:00-05.19 17:00</t>
+          <t>2024.05.25 19:30-05.30 22:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2093</v>
+        <v>71</v>
       </c>
       <c r="G43" t="n">
-        <v>68</v>
+        <v>680</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81766</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Lfxwe5PO1707120983684.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2024.05.18</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>北京·次元风暴游园会2.0</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>安翔路1号院 老故事503文化创意产业园</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2024.05.18 09:00-05.19 17:00</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>6</v>
-      </c>
-      <c r="G44" t="n">
-        <v>55</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81782</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202402/7J276vFp1707191576670.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2024.05.25</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>北京·英文原版音乐剧《剧院魅影续作：真爱永恒》Andrew Lloyd Webber’s  Love Never Dies</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>东直门南大街14号 北京保利剧院</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2024.05.25 19:30-05.30 22:00</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>70</v>
-      </c>
-      <c r="G45" t="n">
-        <v>680</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80957</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/0MQ6YUgo1705474811213.jpeg</t>
         </is>

--- a/北京-漫展信息.xlsx
+++ b/北京-漫展信息.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G6" t="n">
         <v>9.9</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="G8" t="n">
         <v>85</v>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
         <v>66</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G10" t="n">
         <v>48</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G12" t="n">
         <v>93</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
         <v>58</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6393</v>
+        <v>6428</v>
       </c>
       <c r="G15" t="n">
         <v>78</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
         <v>128</v>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>7354</v>
+        <v>7381</v>
       </c>
       <c r="G19" t="n">
         <v>63</v>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G21